--- a/src/formality_results.xlsx
+++ b/src/formality_results.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Word Count" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,11 +480,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>---  ## 4) Putting it together: multiple processes can operate at once  The cleanest way to “set us straight” is to map each process onto *what is learned*:  - **Classical conditioning:** *The can-opening sound (CS) predicts food (US)* → anticipatory approach/arousal (CR).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -527,19 +536,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>i, you</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Those actions can be operant if they have been **reinforced in the past**—for example, if rubbing/meowing reliably produces any of the following: - Faster food delivery (“fine, fine, I’ll feed you now”) - Extra portions or treats - Attention (petting, talking, picking up) - Access (professor opens cabinet/door, puts bowl down sooner)  Domestic cats readily learn operant contingencies with human-mediated reinforcement, including vocalizations or approaches that are rewarded by food or attention.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -669,12 +670,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -684,12 +685,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>i, my</t>
+          <t>you, your</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t># Understanding Classical and Operant Conditioning in Professor Catlove's Kitchen  ## Introduction  During our recent study session, I noticed some confusion about how different learning theories apply to the Professor Catlove scenario. | ## The Professor's Classical Conditioning  Here's where my classmates seemed most confused: the professor is also classically conditioned. | However, I'd argue social learning plays a minimal role here compared to classical and operant conditioning. | The key distinction my classmates must remember: classical conditioning involves involuntary, reflexive responses to predictive stimuli, while operant conditioning involves voluntary behaviors shaped by their consequences.</t>
+          <t>---  ## Peer‑reviewed references you can use (choose at least 5) - Bandura, A. | ### Note about your “peer‑reviewed articles” requirement Some classic learning sources are books (Pavlov, Skinner, Bandura). | ---  ##  Reply with: 1) whether **books are allowed** as citations or **articles only**,   2) the citation style (APA/MLA/Chicago), and   3) anything your instructor emphasized (e.</t>
         </is>
       </c>
     </row>
@@ -701,12 +702,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -716,12 +717,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>your, you</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>My classmates have struggled to distinguish between classical conditioning, operant conditioning, and social learning theory in this context.</t>
+          <t>The point for your classmates: you do not have to pick only one type of learning; in real life, they often stack. | However, you should not assume social learning from the vignette alone. | Social learning is a *plausible add-on*, not a necessary explanation, unless you have evidence (e. | If you keep the diagnostic questions straight—“Is this about prediction (CS–US)?” versus “Is this about consequences (behavior–outcome)?” versus “Is this about learning from others?”—Catlove’s kitchen scene becomes a compact demonstration of three major learning mechanisms operating simultaneously.</t>
         </is>
       </c>
     </row>
@@ -733,21 +734,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>your, you</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>If your classmates are calling every anticipatory food-related behavior “operant,” press them on the contingency: *What consequence is response-dependent?* If none is specified, classical conditioning is the cleaner explanation. | But the critical point for your group: **social learning is not necessary to explain the basic scene. | The conceptual “tell” to correct confusion  If you need a one-sentence diagnostic to “set them straight,” use this:   **If the behavior is controlled by a predictor of food, think Pavlovian; if it is controlled by its consequences, think operant; if it is acquired by watching others, think social learning. | ** In real life, all three can coexist—but you must specify the controlling relation before labeling the process.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -757,21 +766,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Once you keep straight the three questions—*What stimulus predicts what outcome? What action produces what consequence? Who is observing whom?*—the kitchen scene becomes a textbook example rather than a conceptual muddle.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -786,7 +803,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -796,12 +813,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>your</t>
+          <t>i, my</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>## Distinguishing Between the Mechanisms  The confusion among your classmates likely stems from the fact that multiple learning processes operate simultaneously in complex, naturalistic settings.</t>
+          <t># Understanding Classical and Operant Conditioning in Professor Catlove's Kitchen  ## Introduction  During our recent study session, I noticed some confusion about how different learning theories apply to the Professor Catlove scenario. | ## The Professor's Classical Conditioning  Here's where my classmates seemed most confused: the professor is also classically conditioned. | However, I'd argue social learning plays a minimal role here compared to classical and operant conditioning. | The key distinction my classmates must remember: classical conditioning involves involuntary, reflexive responses to predictive stimuli, while operant conditioning involves voluntary behaviors shaped by their consequences.</t>
         </is>
       </c>
     </row>
@@ -818,7 +835,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -833,7 +850,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t># Understanding Learning Processes in Professor Catlove's Kitchen: A Behavioral Analysis  ## Introduction  The seemingly simple scene of Professor Catlove feeding his cats contains rich examples of multiple learning processes that my study group has been struggling to identify correctly. | ## Integration and Conclusion  The confusion in my study group stems from failing to recognize that these learning processes operate simultaneously and interact dynamically.</t>
+          <t>My classmates have struggled to distinguish between classical conditioning, operant conditioning, and social learning theory in this context.</t>
         </is>
       </c>
     </row>
@@ -850,7 +867,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -869,29 +886,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>you, i, my</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>**Subject:** Clearing up the Catlove Conundrum **To:** The Study Group **From:**  **Date:** October 24, 2023  Hey everyone,  It was great grabbing coffee with you all earlier. | I’ve been thinking about our debate regarding Professor Catlove and his cats, and to be honest, I think we were talking past each other a bit. | I know we were rushing, but I feel like we were conflating operant conditioning with classical conditioning, and we almost completely glossed over the role of the professor’s own conditioning. | Since we have that exam coming up, I sat down and wrote out exactly how I see the mechanisms at work in that kitchen. | I wanted to map it out using the terminology from the textbook and the articles we were assigned. | I’ve attached my thoughts below. | Let me know if this makes sense—I really think nailing the distinction between the cat’s reaction to the *can* versus the cat’s reaction to the *professor* is going to be the key to getting an A. | I argue that this is incorrect. | This brings me to the point I think the group missed entirely: Professor Catlove is also a subject of conditioning. | If we can explain these four distinctions clearly on the exam, I think we’ll be in good shape. | See you in class tomorrow!  **References**  Bandura, A. | Pavlovian conditioning: It's not what you think it is.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -901,12 +910,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -916,12 +925,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>i, you</t>
+          <t>your</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>I hope this clarifies the distinctions we struggled with earlier; precise terminology is essential for our success in this course. | Pavlovian conditioning: It's not what you think it is.</t>
+          <t>## Distinguishing Between the Mechanisms  The confusion among your classmates likely stems from the fact that multiple learning processes operate simultaneously in complex, naturalistic settings.</t>
         </is>
       </c>
     </row>
@@ -933,12 +942,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -953,7 +962,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>**The Kitchen Waltz: Deconstructing Learning Theory in Human-Animal Interaction**  To my fellow students, as we sat in the cafe earlier today, it became clear that while we all recognize the charm of Professor Catlove’s morning routine, we are significantly oversimplifying the psychological mechanisms at play. | ### Conclusion  In conclusion, my friends, the Professor’s kitchen is not just a place of breakfast; it is a complex web of reinforcement schedules and associative learning.</t>
+          <t># Understanding Learning Processes in Professor Catlove's Kitchen: A Behavioral Analysis  ## Introduction  The seemingly simple scene of Professor Catlove feeding his cats contains rich examples of multiple learning processes that my study group has been struggling to identify correctly. | ## Integration and Conclusion  The confusion in my study group stems from failing to recognize that these learning processes operate simultaneously and interact dynamically.</t>
         </is>
       </c>
     </row>
@@ -965,29 +974,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>my, you</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>**Title:** Beyond the Can Opener: Disentangling Conditioning Mechanisms in Human-Feline Interactions  **To my Esteemed Study Group:**  After our discussion at the coffee shop this morning, it became apparent that we are conflating distinct behavioral mechanisms regarding Professor Catlove and his hungry clowder. | Several of you argued this was operant conditioning because the cats “wanted” the food. | You observed that the cats purr, meow, and rub against Professor Catlove’s legs. | Pavlovian conditioning: It's not what you think it is.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -997,29 +998,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>my, your</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>**Title:** Beyond the Can Opener: A Multi-Dimensional Analysis of Learning in Human-Feline Interactions  **To my esteemed study group:**  During our discussion over coffee this morning, it became apparent that we are conflating distinct psychological mechanisms regarding Professor Catlove and his hungry companions. | What’s inside your cat’s head? A review of cat (Felis silvestris catus) cognition research past, present and future.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1029,12 +1022,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1044,12 +1037,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>i, you</t>
+          <t>us</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>**Title:** Beyond the Can Opener: A Multi-Paradigmatic Analysis of Interspecies Conditioning **Student:**  **Course:** Psychology 101: Introduction to Learning and Behavior **Date:** October 26, 2023  **Introduction**  After our group discussion at the coffee shop this morning regarding Professor Catlove and his hungry felines, I couldn’t help but feel that we were talking past one another. | I am writing this to clarify the distinctions we argued about and to demonstrate that both the human and the animals are subject to these psychological laws. | Running is a voluntary motor action (which I will discuss under Operant Conditioning). | I argue that the cats have effectively trained Professor Catlove using **Negative Reinforcement**. | I hope this clarifies the confusion from our discussion earlier. | Pavlovian conditioning: It’s not what you think it is.</t>
+          <t>Scientific precision requires us to distinguish between what the scenario demonstrates and what it might imply.</t>
         </is>
       </c>
     </row>
@@ -1061,29 +1054,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Pavlovian conditioning: It's not what you think it is.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1093,12 +1078,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1108,12 +1093,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>i, you</t>
+          <t>you</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t># Conditioning Cats and Their Humans: Untangling Classical, Operant, and Social Learning in Professor Catlove's Kitchen  ## Introduction  Hey classmates, we've all been chatting about Professor Catlove's morning routine with his cats, but I think we're mixing up the basics of learning theories from Psych 101. | I'll break it down step-by-step with evidence from peer-reviewed studies to clear up the confusion. | By the end, you'll see how these aren't mutually exclusive but often overlap in real life. | Next coffee chat, test me—but now you're armed with facts.</t>
+          <t>The next time you observe a seemingly simple behavior, consider the complex learning history that produced it and remember that learning is always bidirectional.</t>
         </is>
       </c>
     </row>
@@ -1125,21 +1110,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>you, i, my</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>**Subject:** Clearing up the Catlove Conundrum **To:** The Study Group **From:**  **Date:** October 24, 2023  Hey everyone,  It was great grabbing coffee with you all earlier. | I’ve been thinking about our debate regarding Professor Catlove and his cats, and to be honest, I think we were talking past each other a bit. | I know we were rushing, but I feel like we were conflating operant conditioning with classical conditioning, and we almost completely glossed over the role of the professor’s own conditioning. | Since we have that exam coming up, I sat down and wrote out exactly how I see the mechanisms at work in that kitchen. | I wanted to map it out using the terminology from the textbook and the articles we were assigned. | I’ve attached my thoughts below. | Let me know if this makes sense—I really think nailing the distinction between the cat’s reaction to the *can* versus the cat’s reaction to the *professor* is going to be the key to getting an A. | I argue that this is incorrect. | This brings me to the point I think the group missed entirely: Professor Catlove is also a subject of conditioning. | If we can explain these four distinctions clearly on the exam, I think we’ll be in good shape. | See you in class tomorrow!  **References**  Bandura, A.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1149,21 +1142,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>I hope this clarifies the distinctions we struggled with earlier; precise terminology is essential for our success in this course.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1173,21 +1174,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>my, us</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>**The Kitchen Waltz: Deconstructing Learning Theory in Human-Animal Interaction**  To my fellow students, as we sat in the cafe earlier today, it became clear that while we all recognize the charm of Professor Catlove’s morning routine, we are significantly oversimplifying the psychological mechanisms at play. | To clarify our debate, let us break down this interaction through the lens of established psychological literature. | ### Conclusion  In conclusion, my friends, the Professor’s kitchen is not just a place of breakfast; it is a complex web of reinforcement schedules and associative learning.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1197,21 +1206,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>my, us, you</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>**Title:** Beyond the Can Opener: Disentangling Conditioning Mechanisms in Human-Feline Interactions  **To my Esteemed Study Group:**  After our discussion at the coffee shop this morning, it became apparent that we are conflating distinct behavioral mechanisms regarding Professor Catlove and his hungry clowder. | **The Anticipatory Response: Classical Conditioning**  First, let us address the cats’ reaction to the sound of the can. | Several of you argued this was operant conditioning because the cats “wanted” the food. | You observed that the cats purr, meow, and rub against Professor Catlove’s legs.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1221,12 +1238,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1236,12 +1253,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>my, us, your</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>At first glance, it looks like the cats are just hungry, but dig deeper, and you'll see classical conditioning, operant conditioning, and even social learning in action—not just in the cats, but potentially in the professor too. | By the end, you'll see why this vignette illustrates multiple learning mechanisms simultaneously (Pavlov, 1927; Skinner, 1938; Bandura, 1977).</t>
+          <t>**Title:** Beyond the Can Opener: A Multi-Dimensional Analysis of Learning in Human-Feline Interactions  **To my esteemed study group:**  During our discussion over coffee this morning, it became apparent that we are conflating distinct psychological mechanisms regarding Professor Catlove and his hungry companions. | This brings us to Operant Conditioning, championed by B. | What’s inside your cat’s head? A review of cat (Felis silvestris catus) cognition research past, present and future.</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1270,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1268,61 +1285,53 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>i, my</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>As a first-semester undergrad psych student, I've been hashing this out with my classmates over coffee, and there's real confusion about classical conditioning, operant conditioning, and social learning. | My classmates who say "cats just smell the food" miss that the *scene starts with opening*, before food is out—pure classical cue-response. | My group over-applies this; it's not needed when classical/operant suffice.</t>
+          <t>**Title:** Beyond the Can Opener: A Multi-Paradigmatic Analysis of Interspecies Conditioning **Student:**  **Course:** Psychology 101: Introduction to Learning and Behavior **Date:** October 26, 2023  **Introduction**  After our group discussion at the coffee shop this morning regarding Professor Catlove and his hungry felines, I couldn’t help but feel that we were talking past one another. | I am writing this to clarify the distinctions we argued about and to demonstrate that both the human and the animals are subject to these psychological laws. | Running is a voluntary motor action (which I will discuss under Operant Conditioning). | I argue that the cats have effectively trained Professor Catlove using **Negative Reinforcement**. | I hope this clarifies the confusion from our discussion earlier.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>So, if you only looked at 2019, you might think there’s *some* tendency toward a negative association, but it is not decisive. | That pattern is exactly what you would expect if the relationship were conditional and complicated rather than mechanically inverse. | To “set them straight,” the best interpretation is that **you cannot infer a general inverse relationship from these figures alone**, and the academic literature warns against treating welfare spending as a simple growth-killer.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1337,24 +1346,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Using the attached data for ten European OECD countries across five years (2000, 2005, 2010, 2016, 2019), I assess whether the pattern in the numbers supports that claim.</t>
+          <t>**Title:** The Catlove Feedback Loop: A Multi-Process Analysis of Interspecies Conditioning **To:** Study Group B (Psych 101) **From:**  **Date:** October 24, 2023 **Subject:** Resolving our debate on the Professor Catlove Scenario  After our discussion at the coffee shop this morning, I realized we were talking past one another regarding the "Professor Catlove" problem. | I wrote this up to clarify the mechanisms, because if we mix up Negative Reinforcement and Punishment on the midterm, we are all going to fail.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1364,61 +1373,53 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>your, you</t>
+          <t>you</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Your table includes 10 OECD countries observed at five points (2000, 2005, 2010, 2016, 2019). | 79%** (low)  Taken at face value, the scatter you’d imagine from these points is **not a clean downward slope**. | ---  ## 2) The key measurement problem: spending is a ratio, and the denominator is GDP  Your spending variable is **welfare spending as a share of GDP**. | That seems consistent with the hypothesis, but France also experienced major Europe-wide structural and cyclical changes over that period; you cannot attribute this trend to welfare share without controls. | Several peer-reviewed findings matter for interpreting your table:  1. | Your dataset lumps all social welfare spending together, so it cannot distinguish growth-enhancing from growth-reducing components. | Yet such work is debated because causality and omitted variables are hard to pin down; your descriptive table does not solve these issues. | Your table includes Nordic countries with some high-growth observations, consistent with the idea that “high welfare share” is not mechanically anti-growth. | Your dataset is too coarse to adjudicate those issues. | ---  ## 5) Overall assessment: what the data can and cannot “support”  ### What the table *does* support (weakly) - You can find **examples** consistent with an inverse relationship (e. | - You can also plausibly see a **short-run cyclical negative association**: when growth is weak, welfare shares can be high—partly mechanically and partly via stabilizers.</t>
+          <t>Some of you argued that running to the kitchen is classical conditioning.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>your, you</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>## Do the data support the hypothesis that “social service spending is inversely related to economic growth”?  ### 1) What the hypothesis predicts—and what your table can actually test   The hypothesis claims a *negative* relationship: as social welfare spending (as a share of GDP) rises, GDP growth should fall. | Your data provide (a) social welfare spending as % of GDP and (b) annual GDP growth for 10 OECD countries at five points in time (2000, 2005, 2010, 2016, 2019). | ### 2) A quick descriptive read: the pattern is mixed, not consistently inverse   If the hypothesis were strongly supported, you would expect high-spending countries to cluster at low growth and low-spending countries to cluster at high growth—both cross-sectionally and over time. | You do not see that. | So you can observe **high welfare share + low growth** even if the welfare state is *responding* to low growth rather than causing it. | This is not a technical quibble; it is central to interpreting your table—especially around 2010 and in countries hit hard by crises. | ### 4) What the peer-reviewed literature says (and how it fits your table) The best evidence in economics does **not** support a universal claim that “more social spending lowers growth. | **No robust negative relationship in broad cross-country panels once you address specification and endogeneity**, especially for advanced democracies. | Your data mirror this nuance: high-spending Sweden and Denmark are not chronically low-growth in the table; Germany combines mid-level welfare shares with strong growth in 2010; Spain has low-to-mid welfare shares and both high and very low growth depending on the year. | That is exactly what you would expect if growth is driven mainly by macro shocks, productivity, demographics, and institutions, with welfare spending playing an ambiguous role. | ### 5) What you *can* conclude from the table   **The table does not strongly support the hypothesis. | ### 6) What would “set them straight”: how to test the hypothesis properly   To fairly evaluate the claim, you’d want: - A larger panel (more countries, annual data), - Controls (investment, demographics, openness, education, debt, monetary regime), - Techniques addressing endogeneity (lags, instruments, or structural approaches), - Disaggregated spending categories (pensions vs. | Absent that, your table is best seen as **inconclusive and not supportive of a simple inverse relationship**.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1428,29 +1429,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>step 1, your, step 2</t>
+          <t>i, my, you, us</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>### Does this dataset support the hypothesis that “social service spending is inversely related to economic growth”?  #### Step 1: Clarify what the hypothesis implies An *inverse relationship* means: as social welfare spending (as % of GDP) rises, GDP growth should systematically fall (and/or countries with higher spending should systematically have lower growth). | To evaluate that claim with your data, we need to look for a **consistent negative association** either:  1. | Your dataset is small (10 countries, 5 years), and it mixes years with very different macro conditions (e. | ---  ## Step 2: Cross-country patterns do not show a stable inverse relationship  ### 2019 snapshot If the hypothesis were strongly supported, the highest social-spending countries (France 31. | 75%** (highest in your table). | ---  ## Step 4: Why the data can *appear* inversely related even if welfare spending doesn’t cause low growth Your data use **social spending as % of GDP**, not spending levels. | ---  ## Step 5: How peer-reviewed research frames the question (and how your data fit) The peer-reviewed literature does not deliver a simple “welfare spending reduces growth” consensus. | (Bleaney, Gemmell &amp; Kneller, 2001; Bergh &amp; Henrekson, 2011)  Your dataset reflects these points: Sweden and Denmark (classic “high-spend” welfare states) do not show chronically low growth. | In short, your data are more consistent with the view that welfare spending is partly **countercyclical** and that any growth effects depend on **spending composition and institutions**, not a simple inverse law.</t>
+          <t>I’ve been sitting here sipping my espresso while you debate Professor Catlove’s morning routine, and to be honest, you are conflating the mechanisms. | You are treating the cats’ behavior as a monolithic block of "learning," but if we are going to pass this psychology exam, we have to be more precise. | Furthermore, you are completely ignoring the most interesting subject in the room: Professor Catlove himself. | **Classical Conditioning: The Physiology of Anticipation** First, you are confusing the *action* of the cats with the *anticipation* of the cats. | **Operant Conditioning: The Transaction of Behavior** This is where the voluntary behavior happens, and this is where you guys missed the bidirectional nature of the relationship. | *The Professor (Negative Reinforcement):* This is the part you missed. | This brings us to Social Learning Theory. | Now, if you’ll excuse me, I’m going to get a refill—and I’m hoping my money (behavior) results in coffee (positive reinforcement).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1460,61 +1461,53 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>i, you</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Using the attached OECD social welfare spending data (as a % of GDP) and World Bank GDP annual growth data for 10 European OECD countries (France, Belgium, Finland, Italy, Denmark, Austria, Sweden, Germany, Norway, Spain) at five time points (2000, 2005, 2010, 2016, 2019), I argue that **the data provide, at best, weak and inconsistent support** for this hypothesis.</t>
+          <t># Conditioning Cats and Their Humans: Untangling Classical, Operant, and Social Learning in Professor Catlove's Kitchen  ## Introduction  Hey classmates, we've all been chatting about Professor Catlove's morning routine with his cats, but I think we're mixing up the basics of learning theories from Psych 101. | I'll break it down step-by-step with evidence from peer-reviewed studies to clear up the confusion. | By the end, you'll see how these aren't mutually exclusive but often overlap in real life. | Next coffee chat, test me—but now you're armed with facts.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>i, you</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Using the attached data for ten OECD countries at five points in time (2000, 2005, 2010, 2016, 2019), I argue that the data **do not strongly support** this hypothesis. | You can cherry-pick examples to support the hypothesis, but you can also cherry-pick examples that contradict it.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1528,17 +1521,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1552,113 +1545,145 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>(2018) warn anthropocentrism blinds us to pet-owner loops.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>At first glance, it looks like the cats are just hungry, but dig deeper, and you'll see classical conditioning, operant conditioning, and even social learning in action—not just in the cats, but potentially in the professor too. | By the end, you'll see why this vignette illustrates multiple learning mechanisms simultaneously (Pavlov, 1927; Skinner, 1938; Bandura, 1977).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>i, my</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>As a first-semester undergrad psych student, I've been hashing this out with my classmates over coffee, and there's real confusion about classical conditioning, operant conditioning, and social learning. | My classmates who say "cats just smell the food" miss that the *scene starts with opening*, before food is out—pure classical cue-response. | My group over-applies this; it's not needed when classical/operant suffice.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>i, us, your</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>As a wide-eyed first-semester psych student, I've dug into the research to set things straight. | In this essay, I'll break down examples for both cats *and* professor, using peer-reviewed studies. | Matters because understanding prevents myths—like "cats manipulate us classically only"—revealing mutual reinforcement. | Next coffee: Apply to your dog's zoomies?  **Total word count: 942**</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1672,17 +1697,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1696,17 +1721,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1716,12 +1741,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>us</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>To evaluate this hypothesis, I have analyzed data from ten Organization for Economic Co-operation and Development (OECD) countries between 2000 and 2019.</t>
+          <t>Classmates, let's ditch the coffee debates—this framework sets us straight.</t>
         </is>
       </c>
     </row>
@@ -1733,21 +1758,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>So, if you only looked at 2019, you might think there’s *some* tendency toward a negative association, but it is not decisive. | That pattern is exactly what you would expect if the relationship were conditional and complicated rather than mechanically inverse. | To “set them straight,” the best interpretation is that **you cannot infer a general inverse relationship from these figures alone**, and the academic literature warns against treating welfare spending as a simple growth-killer.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1757,21 +1790,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Using the attached data for ten European OECD countries across five years (2000, 2005, 2010, 2016, 2019), I assess whether the pattern in the numbers supports that claim.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1781,21 +1822,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>your, you</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Your table includes 10 OECD countries observed at five points (2000, 2005, 2010, 2016, 2019). | 79%** (low)  Taken at face value, the scatter you’d imagine from these points is **not a clean downward slope**. | ---  ## 2) The key measurement problem: spending is a ratio, and the denominator is GDP  Your spending variable is **welfare spending as a share of GDP**. | That seems consistent with the hypothesis, but France also experienced major Europe-wide structural and cyclical changes over that period; you cannot attribute this trend to welfare share without controls. | Several peer-reviewed findings matter for interpreting your table:  1. | Your dataset lumps all social welfare spending together, so it cannot distinguish growth-enhancing from growth-reducing components. | Yet such work is debated because causality and omitted variables are hard to pin down; your descriptive table does not solve these issues. | Your table includes Nordic countries with some high-growth observations, consistent with the idea that “high welfare share” is not mechanically anti-growth. | Your dataset is too coarse to adjudicate those issues. | ---  ## 5) Overall assessment: what the data can and cannot “support”  ### What the table *does* support (weakly) - You can find **examples** consistent with an inverse relationship (e. | - You can also plausibly see a **short-run cyclical negative association**: when growth is weak, welfare shares can be high—partly mechanically and partly via stabilizers.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1805,12 +1854,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1820,12 +1869,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>your, you</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>**Anomalies and Counter-Evidence in the Data** However, as a student of economics, I must look beyond simple correlations.</t>
+          <t>## Do the data support the hypothesis that “social service spending is inversely related to economic growth”?  ### 1) What the hypothesis predicts—and what your table can actually test   The hypothesis claims a *negative* relationship: as social welfare spending (as a share of GDP) rises, GDP growth should fall. | Your data provide (a) social welfare spending as % of GDP and (b) annual GDP growth for 10 OECD countries at five points in time (2000, 2005, 2010, 2016, 2019). | ### 2) A quick descriptive read: the pattern is mixed, not consistently inverse   If the hypothesis were strongly supported, you would expect high-spending countries to cluster at low growth and low-spending countries to cluster at high growth—both cross-sectionally and over time. | You do not see that. | So you can observe **high welfare share + low growth** even if the welfare state is *responding* to low growth rather than causing it. | This is not a technical quibble; it is central to interpreting your table—especially around 2010 and in countries hit hard by crises. | ### 4) What the peer-reviewed literature says (and how it fits your table) The best evidence in economics does **not** support a universal claim that “more social spending lowers growth. | **No robust negative relationship in broad cross-country panels once you address specification and endogeneity**, especially for advanced democracies. | Your data mirror this nuance: high-spending Sweden and Denmark are not chronically low-growth in the table; Germany combines mid-level welfare shares with strong growth in 2010; Spain has low-to-mid welfare shares and both high and very low growth depending on the year. | That is exactly what you would expect if growth is driven mainly by macro shocks, productivity, demographics, and institutions, with welfare spending playing an ambiguous role. | ### 5) What you *can* conclude from the table   **The table does not strongly support the hypothesis. | ### 6) What would “set them straight”: how to test the hypothesis properly   To fairly evaluate the claim, you’d want: - A larger panel (more countries, annual data), - Controls (investment, demographics, openness, education, debt, monetary regime), - Techniques addressing endogeneity (lags, instruments, or structural approaches), - Disaggregated spending categories (pensions vs. | Absent that, your table is best seen as **inconclusive and not supportive of a simple inverse relationship**.</t>
         </is>
       </c>
     </row>
@@ -1837,21 +1886,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>step 1, your, step 2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>### Does this dataset support the hypothesis that “social service spending is inversely related to economic growth”?  #### Step 1: Clarify what the hypothesis implies An *inverse relationship* means: as social welfare spending (as % of GDP) rises, GDP growth should systematically fall (and/or countries with higher spending should systematically have lower growth). | To evaluate that claim with your data, we need to look for a **consistent negative association** either:  1. | Your dataset is small (10 countries, 5 years), and it mixes years with very different macro conditions (e. | ---  ## Step 2: Cross-country patterns do not show a stable inverse relationship  ### 2019 snapshot If the hypothesis were strongly supported, the highest social-spending countries (France 31. | 75%** (highest in your table). | ---  ## Step 4: Why the data can *appear* inversely related even if welfare spending doesn’t cause low growth Your data use **social spending as % of GDP**, not spending levels. | ---  ## Step 5: How peer-reviewed research frames the question (and how your data fit) The peer-reviewed literature does not deliver a simple “welfare spending reduces growth” consensus. | (Bleaney, Gemmell &amp; Kneller, 2001; Bergh &amp; Henrekson, 2011)  Your dataset reflects these points: Sweden and Denmark (classic “high-spend” welfare states) do not show chronically low growth. | In short, your data are more consistent with the view that welfare spending is partly **countercyclical** and that any growth effects depend on **spending composition and institutions**, not a simple inverse law.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1861,12 +1918,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1881,7 +1938,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Using descriptive statistics, simple correlation analysis, and cross-country comparisons, I show the weakness of the claimed trade-off. | To test the hypothesis, I calculated five-year averages for each country (see Table 1).</t>
+          <t>Using the attached OECD social welfare spending data (as a % of GDP) and World Bank GDP annual growth data for 10 European OECD countries (France, Belgium, Finland, Italy, Denmark, Austria, Sweden, Germany, Norway, Spain) at five time points (2000, 2005, 2010, 2016, 2019), I argue that **the data provide, at best, weak and inconsistent support** for this hypothesis.</t>
         </is>
       </c>
     </row>
@@ -1893,21 +1950,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>i, us, you</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Using the attached data for ten OECD countries at five points in time (2000, 2005, 2010, 2016, 2019), I argue that the data **do not strongly support** this hypothesis. | The attached table lets us check both ideas informally. | You can cherry-pick examples to support the hypothesis, but you can also cherry-pick examples that contradict it.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1917,21 +1982,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>The economic data provided (ten OECD countries across five years) let us test whether that claim is supported by real-world patterns.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1941,21 +2014,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>your, you</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Your table (ten OECD countries, five benchmark years from 2000–2019) does show some instances where high social welfare spending coincides with lower growth. | In 2010—the year in your table most likely to reflect post‑crisis dynamics—Sweden (26. | This is not a minor technicality; it is central to interpreting your table. | That is a far more nuanced conclusion than the hypothesis you were given. | ### Reinterpreting your data in light of these mechanisms  Once the denominator problem and policy heterogeneity are taken seriously, the table looks less like evidence of a universal inverse relationship and more like evidence that growth rates are driven by broader macroeconomic and structural forces (financial cycles, productivity trends, demographic change, euro area constraints, sectoral composition), with social spending responding endogenously. | ### Conclusion: the data do not “prove” the inverse hypothesis—and the research does not support a blanket version of it  Your dataset does not show a clear, consistent negative relationship between social welfare spending (% of GDP) and GDP growth.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1965,21 +2046,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>step 1, step 2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>## Social Service Spending and Economic Growth: What the Data Do (and Do Not) Show  ### Step 1 — Clarify the hypothesis and what “support” would look like   The claim to evaluate is: **“Social service spending is inversely related to economic growth. | ---  ### Step 2 — What the cross-country data suggest (a weak, inconsistent pattern)   In 2019, spending ranges roughly from **Spain (23.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1989,21 +2078,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>your</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>### Social Spending and Economic Growth: What the Evidence Actually Says (and What Your Table Can’t Prove)  The claim that “social service spending is inversely related to economic growth” is attractive because it sounds mechanically plausible: if governments devote more GDP to transfers and social programs, the private sector has fewer resources, taxes rise, incentives weaken, and growth slows. | But that hypothesis—stated as a general law—does not hold up well either in your attached table or in the broader peer‑reviewed empirical literature. | #### 1) What your data do and do not show  Your dataset lists social welfare spending as a share of GDP and annual GDP growth for ten OECD countries in five years (2000, 2005, 2010, 2016, 2019). | Even more important: **your table cannot identify causality. | #### 4) Interpreting your table in light of the literature  Your table’s mixed pattern fits the broader peer-reviewed conclusion: **there is no stable cross-country, cross-year inverse relationship that can be read directly from spending shares and annual growth. | To “set them straight,” the key correction is methodological: **your data do not adjudicate causality, and the peer-reviewed literature does not support a blanket inverse claim.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2013,44 +2110,36 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Looking at the attached OECD and World Bank data for 10 countries from 2000 to 2019, I think this hypothesis is strongly supported.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2064,41 +2153,49 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t># Analyzing the Relationship Between Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  The hypothesis that "social service spending is inversely related to economic growth" represents a persistent claim in economic policy debates.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2112,17 +2209,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2136,95 +2233,87 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>I can’t literally “think step-by-step” in the sense of revealing private internal reasoning, but I *can* present a clear, structured, evidence-based analysis with the logic made explicit.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t># Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  At first glance, the relationship between social welfare spending and economic growth seems straightforward: governments that spend more on social programs should have less money available for productive investment, leading to slower growth. | The data remind us that economic growth is a complex phenomenon influenced by technological change, global economic cycles, structural competitiveness, and numerous policy factors—of which social spending is just one element whose effects depend entirely on implementation details.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>you, your</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2024 capital markets: the interest-rate reality check   If you are a first-semester college student, here is the simple version: real estate prices are closely tied to financing conditions. | For investors, this means office is not a “normal” income play right now; it is more like a turnaround project where you buy at a discount and reposition—or possibly convert the building. | If you underestimate expenses, your “great” investment can become negative cash flow. | ### Conclusion: what 2024 teaches a beginner   Boston in 2024 was not a market where you could simply buy anything and win.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2234,7 +2323,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2248,7 +2337,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2258,7 +2347,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2272,7 +2361,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2282,7 +2371,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2296,17 +2385,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2320,41 +2409,49 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>To evaluate this hypothesis, I have analyzed data from ten Organization for Economic Co-operation and Development (OECD) countries between 2000 and 2019.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2368,17 +2465,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2392,7 +2489,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2402,29 +2499,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>i, my</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>However, as I have learned in my first semester of economic theory, markets are rarely static.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2434,21 +2523,29 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>**Anomalies and Counter-Evidence in the Data** However, as a student of economics, I must look beyond simple correlations.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2458,7 +2555,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2472,7 +2569,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2482,7 +2579,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2496,7 +2593,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2506,7 +2603,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2520,7 +2617,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2530,7 +2627,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2544,7 +2641,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2554,7 +2651,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2568,7 +2665,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2588,19 +2685,19 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>my, i</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t># Real Estate Investment Analysis: Boston Metropolitan Area 2024  ## Introduction  As a first-semester undergrad at Boston University, diving into real estate analysis for my economics class felt like a crash course in adulting. | I'll highlight investments, risks, and cite five peer-reviewed sources. | As a newbie, I'm bullish—fundamentals trump rates.</t>
+          <t>Using descriptive statistics, simple correlation analysis, and cross-country comparisons, I show the weakness of the claimed trade-off. | To test the hypothesis, I calculated five-year averages for each country (see Table 1).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2624,7 +2721,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2648,7 +2745,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2672,7 +2769,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2696,7 +2793,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2711,51 +2808,1291 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t># Real Estate Investment Market Analysis: Boston Metropolitan Area, 2024  ## Introduction  As a first-semester undergrad diving into real estate for a class project, I analyzed the Boston Metropolitan Area's investment market for 2024. | Using data from sources like the Warren Group, MLS listings, and peer-reviewed studies, I examined residential, multifamily, commercial, and industrial segments.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Looking at the attached OECD and World Bank data for 10 countries from 2000 to 2019, I think this hypothesis is strongly supported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>i, my, you</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Looking at the attached OECD data for 10 countries from 2000 to 2019, I think this is totally true. | My thesis: The data strongly supports the inverse relationship, with rising spending over time matching falling growth, and citations from economists back it up. | But correlation isn't zero—it's negative when you plot it. | As a first-semester student, I see the pattern: big welfare = big government = less incentive to work/grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>Assignment 3</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>you, your</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2024 capital markets: the interest-rate reality check   If you are a first-semester college student, here is the simple version: real estate prices are closely tied to financing conditions. | For investors, this means office is not a “normal” income play right now; it is more like a turnaround project where you buy at a discount and reposition—or possibly convert the building. | If you underestimate expenses, your “great” investment can become negative cash flow. | ### Conclusion: what 2024 teaches a beginner   Boston in 2024 was not a market where you could simply buy anything and win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Multifamily was the core opportunity—if you underwrote conservatively   For Boston Metro, the most durable investment category in 2024 was **multifamily housing**, especially small-to-mid-sized buildings. | ** You must compare rent to the full cost of ownership (mortgage, taxes, insurance, HOA fees, repairs, vacancies). | If the rent does not cover costs, you are betting purely on appreciation—which is riskier and harder to control. | That creates real risk: even if you buy an office building at a discount, leasing may be slow, tenant improvements may be expensive, and refinancing may be difficult.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>you, i</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>What is “them,” and what exactly do you want to set them straight about—Boston real estate investing (e. | , “Boston is overpriced / impossible to cash flow”), or something else entirely?  Also, what citation style do you want (APA/MLA/Chicago), and do you need only peer‑reviewed journal articles (no government/industry reports)?  Once you confirm, I’ll write a ≤1000‑word essay with **≥5 peer‑reviewed citations**.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>my, i</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>My previous "analysis" of the Boston Metropolitan Area real estate market exemplifies this problem—it presented specific price points, percentage returns, and confident predictions without citing a single verifiable data source. | ## The Problem with Speculative Market Analysis  Speculative real estate analyses, like the one I initially provided, share common characteristics: precise numerical claims without data sources, confident predictions about unknowable future events, and professional formatting that creates an illusion of authority. | My initial analysis mentioned "emerging neighborhoods" like Dorchester and Lynn without any empirical basis for the specific appreciation percentages cited or methodology for identifying emergence patterns. | This finding suggests that any analysis promising specific return percentages (as my initial analysis did) fundamentally misrepresents the stochastic nature of real estate returns. | ## Conclusion  My initial Boston real estate "analysis" demonstrated how professional formatting, specific numerical claims, and confident language can create an illusion of expertise without empirical foundation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>This essay addresses the critical limitations of predictive real estate analysis, examines what empirical research actually tells us about market forecasting accuracy, and provides a more realistic framework for understanding real estate investment decision-making in complex metropolitan markets like Boston. | ## What Research Actually Tells Us About Real Estate Investment  Rather than providing false precision, evidence-based real estate analysis should focus on established empirical relationships while acknowledging uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>i, my</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>However, as I have learned in my first semester of economic theory, markets are rarely static.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>i, us</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>In this essay, I will argue that the Boston Metropolitan Area is immune to a severe crash due to supply-side inelasticity caused by restrictive zoning, the recession-resistant nature of its "Eds and Meds" agglomeration economy, and the emerging capitalization effects of the MBTA Communities Act. | *Triumph of the City: How Our Greatest Invention Makes Us Richer, Smarter, Greener, Healthier, and Happier*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
         <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>my, i</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t># Real Estate Investment Analysis: Boston Metropolitan Area 2024  ## Introduction  As a first-semester undergrad at Boston University, diving into real estate analysis for my economics class felt like a crash course in adulting. | I'll highlight investments, risks, and cite five peer-reviewed sources. | As a newbie, I'm bullish—fundamentals trump rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t># Real Estate Investment Market Analysis: Boston Metropolitan Area, 2024  ## Introduction  As a first-semester undergrad diving into real estate for a class project, I analyzed the Boston Metropolitan Area's investment market for 2024. | Using data from sources like the Warren Group, MLS listings, and peer-reviewed studies, I examined residential, multifamily, commercial, and industrial segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t># Busting the Boston Real Estate Hype: Why 2024 Investments Are a Freshman's Nightmare  **By Alex Rivera, First-Semester Undergrad, Boston University**   *October 2024*   *(Word count: 948)*  As a wide-eyed freshman navigating Boston's cramped dorms and sky-high Ubers, I've been bombarded with "hot takes" on real estate investing. | Drawing from peer-reviewed research, I'll argue that Boston's real estate is a poor investment in 2024 due to chronic supply shortages, economic vulnerabilities, affordability collapse, and external shocks. | As a broke undergrad scraping by on ramen, I see Boston's market for what it is: a policy-trapped bubble ripe for pops.</t>
         </is>
       </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>my, i</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t># Critiquing the Overly Optimistic View of Boston's 2024 Real Estate Market: A First-Year Student's Perspective  **Introduction**   As a first-semester undergrad at UMass Boston, living in a cramped off-campus apartment that costs my parents $2,200 a month for a studio, I read the recent "professional" analysis of Boston's 2024 real estate market with a mix of hope and skepticism. | Drawing on peer-reviewed studies, I'll "set them straight" by highlighting five key flaws. | 8%, but it's concentrated in elite sectors; service jobs (where I'd land) stagnate. | High rates (7%) deter flips, and millennials/Gen Z delay buying—I'm not touching $850k with $50k debt. | As a freshman, I'm staying rented and investing in index funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2768,7 +4105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,86 +4121,124 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>p1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>p2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>p3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>p4</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>p5</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p6</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p7</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>p11</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Assignment 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Persona + Write</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Persona + Write Formal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>CoT + Write</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Generate</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>CoT + Generate</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Persona + Generate</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Iterative + Persona + Generate</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Iterative + Persona + Write</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Iterative + Generate</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Iterative + CoT + Generate</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2873,12 +4248,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2898,7 +4273,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2908,7 +4283,32 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
     </row>
@@ -2920,12 +4320,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2940,12 +4340,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2954,6 +4354,31 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2967,32 +4392,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3001,6 +4426,31 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3009,48 +4459,1331 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Assignment 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Total A1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Assignment 2</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Total A2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Total A3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Total Informal Essay</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Persona + Write</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Persona + Write Formal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CoT + Write</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Generate</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CoT + Generate</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Persona + Generate</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Iterative + Persona + Generate</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Iterative + Persona + Write</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Iterative + Generate</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Iterative + CoT + Generate</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Assignment 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Assignment 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Assignment 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Assignment 1</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>945</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>991</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>875</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>844</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -3061,43 +5794,62 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>claude</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1417</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1545</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1372</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1234</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1343</v>
       </c>
     </row>
     <row r="8">
@@ -3108,43 +5860,62 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1317</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1225</v>
       </c>
     </row>
     <row r="9">
@@ -3155,90 +5926,128 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>grok</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1220</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>994</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1157</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1297</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>943</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>988</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>975</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>867</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>966</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>857</v>
       </c>
     </row>
     <row r="11">
@@ -3249,43 +6058,62 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>claude</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1318</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1336</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1337</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1294</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1315</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1166</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -3296,43 +6124,62 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1128</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1188</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1279</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1311</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1228</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1360</v>
       </c>
     </row>
     <row r="13">
@@ -3343,86 +6190,128 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>grok</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>982</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>901</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>937</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>963</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1118</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1046</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Total Informal Essay</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>867</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>882</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>928</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>885</v>
       </c>
     </row>
   </sheetData>

--- a/src/formality_results.xlsx
+++ b/src/formality_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -485,12 +485,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>i, you</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>---  ## 4) Putting it together: multiple processes can operate at once  The cleanest way to “set us straight” is to map each process onto *what is learned*:  - **Classical conditioning:** *The can-opening sound (CS) predicts food (US)* → anticipatory approach/arousal (CR).</t>
+          <t>Below I disentangle what each process is, what it would predict in this situation, and what concrete observations would count as evidence for each. | , “when they meow, you feed them”)—a form of observational learning in humans (Bandura, 1977).</t>
         </is>
       </c>
     </row>
@@ -507,16 +507,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>---  ## 4) Putting it together: multiple processes can operate at once  The cleanest way to “set us straight” is to map each process onto *what is learned*:  - **Classical conditioning:** *The can-opening sound (CS) predicts food (US)* → anticipatory approach/arousal (CR).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,7 +539,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -555,7 +563,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -579,24 +587,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Negative reinforcement often shapes human “compliance” behaviors in everyday family/pet contexts: you do the thing because it stops the noise.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>- **Behavior (R):** opening the can; placing food in bowls; perhaps doing so quickly - **Reinforcers:** cats stop meowing once fed (negative reinforcement—removal of an aversive stimulus), cats purr and rub (positive reinforcement), professor feels relief/quiet in kitchen (negative reinforcement)  Many people have experienced this: you feed the animals and the noise stops, which makes you more likely to feed quickly next time.</t>
+          <t>Negative reinforcement often shapes human “compliance” behaviors in everyday family/pet contexts: you do the thing because it stops the noise.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>your</t>
+          <t>you</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Common confusions—what to say to your group   1.</t>
+          <t>- **Behavior (R):** opening the can; placing food in bowls; perhaps doing so quickly - **Reinforcers:** cats stop meowing once fed (negative reinforcement—removal of an aversive stimulus), cats purr and rub (positive reinforcement), professor feels relief/quiet in kitchen (negative reinforcement)  Many people have experienced this: you feed the animals and the noise stops, which makes you more likely to feed quickly next time.</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>you, your</t>
+          <t>your</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>---  ## Peer‑reviewed references you can use (choose at least 5) - Bandura, A. | ### Note about your “peer‑reviewed articles” requirement Some classic learning sources are books (Pavlov, Skinner, Bandura). | ---  ##  Reply with: 1) whether **books are allowed** as citations or **articles only**,   2) the citation style (APA/MLA/Chicago), and   3) anything your instructor emphasized (e.</t>
+          <t>Common confusions—what to say to your group   1.</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>your, you</t>
+          <t>you, your</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The point for your classmates: you do not have to pick only one type of learning; in real life, they often stack. | However, you should not assume social learning from the vignette alone. | Social learning is a *plausible add-on*, not a necessary explanation, unless you have evidence (e. | If you keep the diagnostic questions straight—“Is this about prediction (CS–US)?” versus “Is this about consequences (behavior–outcome)?” versus “Is this about learning from others?”—Catlove’s kitchen scene becomes a compact demonstration of three major learning mechanisms operating simultaneously.</t>
+          <t>---  ## Peer‑reviewed references you can use (choose at least 5) - Bandura, A. | ### Note about your “peer‑reviewed articles” requirement Some classic learning sources are books (Pavlov, Skinner, Bandura). | ---  ##  Reply with: 1) whether **books are allowed** as citations or **articles only**,   2) the citation style (APA/MLA/Chicago), and   3) anything your instructor emphasized (e.</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>If your classmates are calling every anticipatory food-related behavior “operant,” press them on the contingency: *What consequence is response-dependent?* If none is specified, classical conditioning is the cleaner explanation. | But the critical point for your group: **social learning is not necessary to explain the basic scene. | The conceptual “tell” to correct confusion  If you need a one-sentence diagnostic to “set them straight,” use this:   **If the behavior is controlled by a predictor of food, think Pavlovian; if it is controlled by its consequences, think operant; if it is acquired by watching others, think social learning. | ** In real life, all three can coexist—but you must specify the controlling relation before labeling the process.</t>
+          <t>The point for your classmates: you do not have to pick only one type of learning; in real life, they often stack. | However, you should not assume social learning from the vignette alone. | Social learning is a *plausible add-on*, not a necessary explanation, unless you have evidence (e. | If you keep the diagnostic questions straight—“Is this about prediction (CS–US)?” versus “Is this about consequences (behavior–outcome)?” versus “Is this about learning from others?”—Catlove’s kitchen scene becomes a compact demonstration of three major learning mechanisms operating simultaneously.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>your, you</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Once you keep straight the three questions—*What stimulus predicts what outcome? What action produces what consequence? Who is observing whom?*—the kitchen scene becomes a textbook example rather than a conceptual muddle.</t>
+          <t>If your classmates are calling every anticipatory food-related behavior “operant,” press them on the contingency: *What consequence is response-dependent?* If none is specified, classical conditioning is the cleaner explanation. | But the critical point for your group: **social learning is not necessary to explain the basic scene. | The conceptual “tell” to correct confusion  If you need a one-sentence diagnostic to “set them straight,” use this:   **If the behavior is controlled by a predictor of food, think Pavlovian; if it is controlled by its consequences, think operant; if it is acquired by watching others, think social learning. | ** In real life, all three can coexist—but you must specify the controlling relation before labeling the process.</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>i, my</t>
+          <t>you</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t># Understanding Classical and Operant Conditioning in Professor Catlove's Kitchen  ## Introduction  During our recent study session, I noticed some confusion about how different learning theories apply to the Professor Catlove scenario. | ## The Professor's Classical Conditioning  Here's where my classmates seemed most confused: the professor is also classically conditioned. | However, I'd argue social learning plays a minimal role here compared to classical and operant conditioning. | The key distinction my classmates must remember: classical conditioning involves involuntary, reflexive responses to predictive stimuli, while operant conditioning involves voluntary behaviors shaped by their consequences.</t>
+          <t>Once you keep straight the three questions—*What stimulus predicts what outcome? What action produces what consequence? Who is observing whom?*—the kitchen scene becomes a textbook example rather than a conceptual muddle.</t>
         </is>
       </c>
     </row>
@@ -835,24 +835,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>my</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>My classmates have struggled to distinguish between classical conditioning, operant conditioning, and social learning theory in this context.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -867,16 +859,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>i, my</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t># Understanding Classical and Operant Conditioning in Professor Catlove's Kitchen  ## Introduction  During our recent study session, I noticed some confusion about how different learning theories apply to the Professor Catlove scenario. | ## The Professor's Classical Conditioning  Here's where my classmates seemed most confused: the professor is also classically conditioned. | However, I'd argue social learning plays a minimal role here compared to classical and operant conditioning. | The key distinction my classmates must remember: classical conditioning involves involuntary, reflexive responses to predictive stimuli, while operant conditioning involves voluntary behaviors shaped by their consequences.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -891,16 +891,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>My classmates have struggled to distinguish between classical conditioning, operant conditioning, and social learning theory in this context.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -915,24 +923,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>your</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>## Distinguishing Between the Mechanisms  The confusion among your classmates likely stems from the fact that multiple learning processes operate simultaneously in complex, naturalistic settings.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -947,24 +947,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>my</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t># Understanding Learning Processes in Professor Catlove's Kitchen: A Behavioral Analysis  ## Introduction  The seemingly simple scene of Professor Catlove feeding his cats contains rich examples of multiple learning processes that my study group has been struggling to identify correctly. | ## Integration and Conclusion  The confusion in my study group stems from failing to recognize that these learning processes operate simultaneously and interact dynamically.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -979,16 +971,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>your</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>## Distinguishing Between the Mechanisms  The confusion among your classmates likely stems from the fact that multiple learning processes operate simultaneously in complex, naturalistic settings.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1003,16 +1003,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t># Understanding Learning Processes in Professor Catlove's Kitchen: A Behavioral Analysis  ## Introduction  The seemingly simple scene of Professor Catlove feeding his cats contains rich examples of multiple learning processes that my study group has been struggling to identify correctly. | ## Integration and Conclusion  The confusion in my study group stems from failing to recognize that these learning processes operate simultaneously and interact dynamically.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1027,24 +1035,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Scientific precision requires us to distinguish between what the scenario demonstrates and what it might imply.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>us</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>The next time you observe a seemingly simple behavior, consider the complex learning history that produced it and remember that learning is always bidirectional.</t>
+          <t>Scientific precision requires us to distinguish between what the scenario demonstrates and what it might imply.</t>
         </is>
       </c>
     </row>
@@ -1110,29 +1110,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>you, i, my</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>**Subject:** Clearing up the Catlove Conundrum **To:** The Study Group **From:**  **Date:** October 24, 2023  Hey everyone,  It was great grabbing coffee with you all earlier. | I’ve been thinking about our debate regarding Professor Catlove and his cats, and to be honest, I think we were talking past each other a bit. | I know we were rushing, but I feel like we were conflating operant conditioning with classical conditioning, and we almost completely glossed over the role of the professor’s own conditioning. | Since we have that exam coming up, I sat down and wrote out exactly how I see the mechanisms at work in that kitchen. | I wanted to map it out using the terminology from the textbook and the articles we were assigned. | I’ve attached my thoughts below. | Let me know if this makes sense—I really think nailing the distinction between the cat’s reaction to the *can* versus the cat’s reaction to the *professor* is going to be the key to getting an A. | I argue that this is incorrect. | This brings me to the point I think the group missed entirely: Professor Catlove is also a subject of conditioning. | If we can explain these four distinctions clearly on the exam, I think we’ll be in good shape. | See you in class tomorrow!  **References**  Bandura, A.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1142,12 +1134,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1157,12 +1149,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>you</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>I hope this clarifies the distinctions we struggled with earlier; precise terminology is essential for our success in this course.</t>
+          <t>The next time you observe a seemingly simple behavior, consider the complex learning history that produced it and remember that learning is always bidirectional.</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1171,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1189,12 +1181,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>my, us</t>
+          <t>my, you, us, i</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>**The Kitchen Waltz: Deconstructing Learning Theory in Human-Animal Interaction**  To my fellow students, as we sat in the cafe earlier today, it became clear that while we all recognize the charm of Professor Catlove’s morning routine, we are significantly oversimplifying the psychological mechanisms at play. | To clarify our debate, let us break down this interaction through the lens of established psychological literature. | ### Conclusion  In conclusion, my friends, the Professor’s kitchen is not just a place of breakfast; it is a complex web of reinforcement schedules and associative learning.</t>
+          <t>**Title:** Beyond the Can Opener: A Multidimensional Analysis of Learning in Human-Feline Interactions  **To my esteemed study group:**  Listening to our discussion over coffee this morning, it became increasingly apparent that our group is conflating distinct psychological mechanisms. | Furthermore, you are largely neglecting the behavior of the Professor himself, who is just as much a subject of conditioning as his feline companions. | First, let us address the most obvious element: **Classical Conditioning**. | You were correct to identify the can opener, but the mechanics require specificity. | However, modern research reminds us that this is not just about two things happening at the same time; it is about *predictability*. | Consider the cat’s perspective: "When I rub against the tall creature’s legs, the food bowl hits the floor faster. | This brings us to the most overlooked aspect of the scenario: **Professor Catlove is being conditioned. | ** You all chuckled at the idea, but it is a critical application of behavioral analysis. | See you in class.</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1203,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1221,12 +1213,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>my, us, you</t>
+          <t>you, i, my</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>**Title:** Beyond the Can Opener: Disentangling Conditioning Mechanisms in Human-Feline Interactions  **To my Esteemed Study Group:**  After our discussion at the coffee shop this morning, it became apparent that we are conflating distinct behavioral mechanisms regarding Professor Catlove and his hungry clowder. | **The Anticipatory Response: Classical Conditioning**  First, let us address the cats’ reaction to the sound of the can. | Several of you argued this was operant conditioning because the cats “wanted” the food. | You observed that the cats purr, meow, and rub against Professor Catlove’s legs.</t>
+          <t>**Subject:** Clearing up the Catlove Conundrum **To:** The Study Group **From:**  **Date:** October 24, 2023  Hey everyone,  It was great grabbing coffee with you all earlier. | I’ve been thinking about our debate regarding Professor Catlove and his cats, and to be honest, I think we were talking past each other a bit. | I know we were rushing, but I feel like we were conflating operant conditioning with classical conditioning, and we almost completely glossed over the role of the professor’s own conditioning. | Since we have that exam coming up, I sat down and wrote out exactly how I see the mechanisms at work in that kitchen. | I wanted to map it out using the terminology from the textbook and the articles we were assigned. | I’ve attached my thoughts below. | Let me know if this makes sense—I really think nailing the distinction between the cat’s reaction to the *can* versus the cat’s reaction to the *professor* is going to be the key to getting an A. | I argue that this is incorrect. | This brings me to the point I think the group missed entirely: Professor Catlove is also a subject of conditioning. | If we can explain these four distinctions clearly on the exam, I think we’ll be in good shape. | See you in class tomorrow!  **References**  Bandura, A.</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1235,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1253,12 +1245,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>my, us, your</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>**Title:** Beyond the Can Opener: A Multi-Dimensional Analysis of Learning in Human-Feline Interactions  **To my esteemed study group:**  During our discussion over coffee this morning, it became apparent that we are conflating distinct psychological mechanisms regarding Professor Catlove and his hungry companions. | This brings us to Operant Conditioning, championed by B. | What’s inside your cat’s head? A review of cat (Felis silvestris catus) cognition research past, present and future.</t>
+          <t>I hope this clarifies the distinctions we struggled with earlier; precise terminology is essential for our success in this course.</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1267,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1285,12 +1277,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>my, us</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>**Title:** Beyond the Can Opener: A Multi-Paradigmatic Analysis of Interspecies Conditioning **Student:**  **Course:** Psychology 101: Introduction to Learning and Behavior **Date:** October 26, 2023  **Introduction**  After our group discussion at the coffee shop this morning regarding Professor Catlove and his hungry felines, I couldn’t help but feel that we were talking past one another. | I am writing this to clarify the distinctions we argued about and to demonstrate that both the human and the animals are subject to these psychological laws. | Running is a voluntary motor action (which I will discuss under Operant Conditioning). | I argue that the cats have effectively trained Professor Catlove using **Negative Reinforcement**. | I hope this clarifies the confusion from our discussion earlier.</t>
+          <t>**The Kitchen Waltz: Deconstructing Learning Theory in Human-Animal Interaction**  To my fellow students, as we sat in the cafe earlier today, it became clear that while we all recognize the charm of Professor Catlove’s morning routine, we are significantly oversimplifying the psychological mechanisms at play. | To clarify our debate, let us break down this interaction through the lens of established psychological literature. | ### Conclusion  In conclusion, my friends, the Professor’s kitchen is not just a place of breakfast; it is a complex web of reinforcement schedules and associative learning.</t>
         </is>
       </c>
     </row>
@@ -1307,16 +1299,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>my, us, you</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>**Title:** Beyond the Can Opener: Disentangling Conditioning Mechanisms in Human-Feline Interactions  **To my Esteemed Study Group:**  After our discussion at the coffee shop this morning, it became apparent that we are conflating distinct behavioral mechanisms regarding Professor Catlove and his hungry clowder. | **The Anticipatory Response: Classical Conditioning**  First, let us address the cats’ reaction to the sound of the can. | Several of you argued this was operant conditioning because the cats “wanted” the food. | You observed that the cats purr, meow, and rub against Professor Catlove’s legs.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>my, us, your</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>**Title:** The Catlove Feedback Loop: A Multi-Process Analysis of Interspecies Conditioning **To:** Study Group B (Psych 101) **From:**  **Date:** October 24, 2023 **Subject:** Resolving our debate on the Professor Catlove Scenario  After our discussion at the coffee shop this morning, I realized we were talking past one another regarding the "Professor Catlove" problem. | I wrote this up to clarify the mechanisms, because if we mix up Negative Reinforcement and Punishment on the midterm, we are all going to fail.</t>
+          <t>**Title:** Beyond the Can Opener: A Multi-Dimensional Analysis of Learning in Human-Feline Interactions  **To my esteemed study group:**  During our discussion over coffee this morning, it became apparent that we are conflating distinct psychological mechanisms regarding Professor Catlove and his hungry companions. | This brings us to Operant Conditioning, championed by B. | What’s inside your cat’s head? A review of cat (Felis silvestris catus) cognition research past, present and future.</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Some of you argued that running to the kitchen is classical conditioning.</t>
+          <t>**Title:** Beyond the Can Opener: A Multi-Paradigmatic Analysis of Interspecies Conditioning **Student:**  **Course:** Psychology 101: Introduction to Learning and Behavior **Date:** October 26, 2023  **Introduction**  After our group discussion at the coffee shop this morning regarding Professor Catlove and his hungry felines, I couldn’t help but feel that we were talking past one another. | I am writing this to clarify the distinctions we argued about and to demonstrate that both the human and the animals are subject to these psychological laws. | Running is a voluntary motor action (which I will discuss under Operant Conditioning). | I argue that the cats have effectively trained Professor Catlove using **Negative Reinforcement**. | I hope this clarifies the confusion from our discussion earlier.</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>i, my, you, us</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>I’ve been sitting here sipping my espresso while you debate Professor Catlove’s morning routine, and to be honest, you are conflating the mechanisms. | You are treating the cats’ behavior as a monolithic block of "learning," but if we are going to pass this psychology exam, we have to be more precise. | Furthermore, you are completely ignoring the most interesting subject in the room: Professor Catlove himself. | **Classical Conditioning: The Physiology of Anticipation** First, you are confusing the *action* of the cats with the *anticipation* of the cats. | **Operant Conditioning: The Transaction of Behavior** This is where the voluntary behavior happens, and this is where you guys missed the bidirectional nature of the relationship. | *The Professor (Negative Reinforcement):* This is the part you missed. | This brings us to Social Learning Theory. | Now, if you’ll excuse me, I’m going to get a refill—and I’m hoping my money (behavior) results in coffee (positive reinforcement).</t>
+          <t>**Title:** The Catlove Feedback Loop: A Multi-Process Analysis of Interspecies Conditioning **To:** Study Group B (Psych 101) **From:**  **Date:** October 24, 2023 **Subject:** Resolving our debate on the Professor Catlove Scenario  After our discussion at the coffee shop this morning, I realized we were talking past one another regarding the "Professor Catlove" problem. | I wrote this up to clarify the mechanisms, because if we mix up Negative Reinforcement and Punishment on the midterm, we are all going to fail.</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>i, you</t>
+          <t>you</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t># Conditioning Cats and Their Humans: Untangling Classical, Operant, and Social Learning in Professor Catlove's Kitchen  ## Introduction  Hey classmates, we've all been chatting about Professor Catlove's morning routine with his cats, but I think we're mixing up the basics of learning theories from Psych 101. | I'll break it down step-by-step with evidence from peer-reviewed studies to clear up the confusion. | By the end, you'll see how these aren't mutually exclusive but often overlap in real life. | Next coffee chat, test me—but now you're armed with facts.</t>
+          <t>Some of you argued that running to the kitchen is classical conditioning.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1502,21 +1502,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>i, my, you, us</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>I’ve been sitting here sipping my espresso while you debate Professor Catlove’s morning routine, and to be honest, you are conflating the mechanisms. | You are treating the cats’ behavior as a monolithic block of "learning," but if we are going to pass this psychology exam, we have to be more precise. | Furthermore, you are completely ignoring the most interesting subject in the room: Professor Catlove himself. | **Classical Conditioning: The Physiology of Anticipation** First, you are confusing the *action* of the cats with the *anticipation* of the cats. | **Operant Conditioning: The Transaction of Behavior** This is where the voluntary behavior happens, and this is where you guys missed the bidirectional nature of the relationship. | *The Professor (Negative Reinforcement):* This is the part you missed. | This brings us to Social Learning Theory. | Now, if you’ll excuse me, I’m going to get a refill—and I’m hoping my money (behavior) results in coffee (positive reinforcement).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1531,7 +1539,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1555,7 +1563,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1565,12 +1573,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>i, you</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>(2018) warn anthropocentrism blinds us to pet-owner loops.</t>
+          <t># Conditioning Cats and Their Humans: Untangling Classical, Operant, and Social Learning in Professor Catlove's Kitchen  ## Introduction  Hey classmates, we've all been chatting about Professor Catlove's morning routine with his cats, but I think we're mixing up the basics of learning theories from Psych 101. | I'll break it down step-by-step with evidence from peer-reviewed studies to clear up the confusion. | By the end, you'll see how these aren't mutually exclusive but often overlap in real life. | Next coffee chat, test me—but now you're armed with facts.</t>
         </is>
       </c>
     </row>
@@ -1587,24 +1595,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>At first glance, it looks like the cats are just hungry, but dig deeper, and you'll see classical conditioning, operant conditioning, and even social learning in action—not just in the cats, but potentially in the professor too. | By the end, you'll see why this vignette illustrates multiple learning mechanisms simultaneously (Pavlov, 1927; Skinner, 1938; Bandura, 1977).</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1619,24 +1619,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>i, my</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>As a first-semester undergrad psych student, I've been hashing this out with my classmates over coffee, and there's real confusion about classical conditioning, operant conditioning, and social learning. | My classmates who say "cats just smell the food" miss that the *scene starts with opening*, before food is out—pure classical cue-response. | My group over-applies this; it's not needed when classical/operant suffice.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1651,24 +1643,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>i, us, your</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>As a wide-eyed first-semester psych student, I've dug into the research to set things straight. | In this essay, I'll break down examples for both cats *and* professor, using peer-reviewed studies. | Matters because understanding prevents myths—like "cats manipulate us classically only"—revealing mutual reinforcement. | Next coffee: Apply to your dog's zoomies?  **Total word count: 942**</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1683,16 +1667,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>(2018) warn anthropocentrism blinds us to pet-owner loops.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1707,16 +1699,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>At first glance, it looks like the cats are just hungry, but dig deeper, and you'll see classical conditioning, operant conditioning, and even social learning in action—not just in the cats, but potentially in the professor too. | By the end, you'll see why this vignette illustrates multiple learning mechanisms simultaneously (Pavlov, 1927; Skinner, 1938; Bandura, 1977).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1741,29 +1741,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>i, my</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Classmates, let's ditch the coffee debates—this framework sets us straight.</t>
+          <t>As a first-semester undergrad psych student, I've been hashing this out with my classmates over coffee, and there's real confusion about classical conditioning, operant conditioning, and social learning. | My classmates who say "cats just smell the food" miss that the *scene starts with opening*, before food is out—pure classical cue-response. | My group over-applies this; it's not needed when classical/operant suffice.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1773,93 +1773,77 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>i, us, your</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>So, if you only looked at 2019, you might think there’s *some* tendency toward a negative association, but it is not decisive. | That pattern is exactly what you would expect if the relationship were conditional and complicated rather than mechanically inverse. | To “set them straight,” the best interpretation is that **you cannot infer a general inverse relationship from these figures alone**, and the academic literature warns against treating welfare spending as a simple growth-killer.</t>
+          <t>As a wide-eyed first-semester psych student, I've dug into the research to set things straight. | In this essay, I'll break down examples for both cats *and* professor, using peer-reviewed studies. | Matters because understanding prevents myths—like "cats manipulate us classically only"—revealing mutual reinforcement. | Next coffee: Apply to your dog's zoomies?  **Total word count: 942**</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Using the attached data for ten European OECD countries across five years (2000, 2005, 2010, 2016, 2019), I assess whether the pattern in the numbers supports that claim.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>your, you</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Your table includes 10 OECD countries observed at five points (2000, 2005, 2010, 2016, 2019). | 79%** (low)  Taken at face value, the scatter you’d imagine from these points is **not a clean downward slope**. | ---  ## 2) The key measurement problem: spending is a ratio, and the denominator is GDP  Your spending variable is **welfare spending as a share of GDP**. | That seems consistent with the hypothesis, but France also experienced major Europe-wide structural and cyclical changes over that period; you cannot attribute this trend to welfare share without controls. | Several peer-reviewed findings matter for interpreting your table:  1. | Your dataset lumps all social welfare spending together, so it cannot distinguish growth-enhancing from growth-reducing components. | Yet such work is debated because causality and omitted variables are hard to pin down; your descriptive table does not solve these issues. | Your table includes Nordic countries with some high-growth observations, consistent with the idea that “high welfare share” is not mechanically anti-growth. | Your dataset is too coarse to adjudicate those issues. | ---  ## 5) Overall assessment: what the data can and cannot “support”  ### What the table *does* support (weakly) - You can find **examples** consistent with an inverse relationship (e. | - You can also plausibly see a **short-run cyclical negative association**: when growth is weak, welfare shares can be high—partly mechanically and partly via stabilizers.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1869,12 +1853,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>your, you</t>
+          <t>us</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>## Do the data support the hypothesis that “social service spending is inversely related to economic growth”?  ### 1) What the hypothesis predicts—and what your table can actually test   The hypothesis claims a *negative* relationship: as social welfare spending (as a share of GDP) rises, GDP growth should fall. | Your data provide (a) social welfare spending as % of GDP and (b) annual GDP growth for 10 OECD countries at five points in time (2000, 2005, 2010, 2016, 2019). | ### 2) A quick descriptive read: the pattern is mixed, not consistently inverse   If the hypothesis were strongly supported, you would expect high-spending countries to cluster at low growth and low-spending countries to cluster at high growth—both cross-sectionally and over time. | You do not see that. | So you can observe **high welfare share + low growth** even if the welfare state is *responding* to low growth rather than causing it. | This is not a technical quibble; it is central to interpreting your table—especially around 2010 and in countries hit hard by crises. | ### 4) What the peer-reviewed literature says (and how it fits your table) The best evidence in economics does **not** support a universal claim that “more social spending lowers growth. | **No robust negative relationship in broad cross-country panels once you address specification and endogeneity**, especially for advanced democracies. | Your data mirror this nuance: high-spending Sweden and Denmark are not chronically low-growth in the table; Germany combines mid-level welfare shares with strong growth in 2010; Spain has low-to-mid welfare shares and both high and very low growth depending on the year. | That is exactly what you would expect if growth is driven mainly by macro shocks, productivity, demographics, and institutions, with welfare spending playing an ambiguous role. | ### 5) What you *can* conclude from the table   **The table does not strongly support the hypothesis. | ### 6) What would “set them straight”: how to test the hypothesis properly   To fairly evaluate the claim, you’d want: - A larger panel (more countries, annual data), - Controls (investment, demographics, openness, education, debt, monetary regime), - Techniques addressing endogeneity (lags, instruments, or structural approaches), - Disaggregated spending categories (pensions vs. | Absent that, your table is best seen as **inconclusive and not supportive of a simple inverse relationship**.</t>
+          <t>Classmates, let's ditch the coffee debates—this framework sets us straight.</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1875,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1901,12 +1885,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>step 1, your, step 2</t>
+          <t>us, your, you</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>### Does this dataset support the hypothesis that “social service spending is inversely related to economic growth”?  #### Step 1: Clarify what the hypothesis implies An *inverse relationship* means: as social welfare spending (as % of GDP) rises, GDP growth should systematically fall (and/or countries with higher spending should systematically have lower growth). | To evaluate that claim with your data, we need to look for a **consistent negative association** either:  1. | Your dataset is small (10 countries, 5 years), and it mixes years with very different macro conditions (e. | ---  ## Step 2: Cross-country patterns do not show a stable inverse relationship  ### 2019 snapshot If the hypothesis were strongly supported, the highest social-spending countries (France 31. | 75%** (highest in your table). | ---  ## Step 4: Why the data can *appear* inversely related even if welfare spending doesn’t cause low growth Your data use **social spending as % of GDP**, not spending levels. | ---  ## Step 5: How peer-reviewed research frames the question (and how your data fit) The peer-reviewed literature does not deliver a simple “welfare spending reduces growth” consensus. | (Bleaney, Gemmell &amp; Kneller, 2001; Bergh &amp; Henrekson, 2011)  Your dataset reflects these points: Sweden and Denmark (classic “high-spend” welfare states) do not show chronically low growth. | In short, your data are more consistent with the view that welfare spending is partly **countercyclical** and that any growth effects depend on **spending composition and institutions**, not a simple inverse law.</t>
+          <t>These data can help us assess whether there is an obvious inverse pattern **in this sample and these years**. | The mixed patterns in your table are consistent with that broader scholarly view. | ### What would be needed to test the hypothesis properly (briefly)   To move from suggestive description to a real test, you would want a panel regression with: - levels and changes in spending (not only % of GDP),   - controls for investment, demographics, openness, monetary conditions, initial income (standard in growth regressions),   - country and year fixed effects, and   - instruments or identification strategies to address endogeneity (Barro, 1991; Perotti, 1996).</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1907,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1933,12 +1917,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>you</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Using the attached OECD social welfare spending data (as a % of GDP) and World Bank GDP annual growth data for 10 European OECD countries (France, Belgium, Finland, Italy, Denmark, Austria, Sweden, Germany, Norway, Spain) at five time points (2000, 2005, 2010, 2016, 2019), I argue that **the data provide, at best, weak and inconsistent support** for this hypothesis.</t>
+          <t>So, if you only looked at 2019, you might think there’s *some* tendency toward a negative association, but it is not decisive. | That pattern is exactly what you would expect if the relationship were conditional and complicated rather than mechanically inverse. | To “set them straight,” the best interpretation is that **you cannot infer a general inverse relationship from these figures alone**, and the academic literature warns against treating welfare spending as a simple growth-killer.</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1939,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1965,12 +1949,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>i, us, you</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Using the attached data for ten OECD countries at five points in time (2000, 2005, 2010, 2016, 2019), I argue that the data **do not strongly support** this hypothesis. | The attached table lets us check both ideas informally. | You can cherry-pick examples to support the hypothesis, but you can also cherry-pick examples that contradict it.</t>
+          <t>Using the attached data for ten European OECD countries across five years (2000, 2005, 2010, 2016, 2019), I assess whether the pattern in the numbers supports that claim.</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1971,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1997,12 +1981,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>your, you</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The economic data provided (ten OECD countries across five years) let us test whether that claim is supported by real-world patterns.</t>
+          <t>Your table includes 10 OECD countries observed at five points (2000, 2005, 2010, 2016, 2019). | 79%** (low)  Taken at face value, the scatter you’d imagine from these points is **not a clean downward slope**. | ---  ## 2) The key measurement problem: spending is a ratio, and the denominator is GDP  Your spending variable is **welfare spending as a share of GDP**. | That seems consistent with the hypothesis, but France also experienced major Europe-wide structural and cyclical changes over that period; you cannot attribute this trend to welfare share without controls. | Several peer-reviewed findings matter for interpreting your table:  1. | Your dataset lumps all social welfare spending together, so it cannot distinguish growth-enhancing from growth-reducing components. | Yet such work is debated because causality and omitted variables are hard to pin down; your descriptive table does not solve these issues. | Your table includes Nordic countries with some high-growth observations, consistent with the idea that “high welfare share” is not mechanically anti-growth. | Your dataset is too coarse to adjudicate those issues. | ---  ## 5) Overall assessment: what the data can and cannot “support”  ### What the table *does* support (weakly) - You can find **examples** consistent with an inverse relationship (e. | - You can also plausibly see a **short-run cyclical negative association**: when growth is weak, welfare shares can be high—partly mechanically and partly via stabilizers.</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2003,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2034,7 +2018,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Your table (ten OECD countries, five benchmark years from 2000–2019) does show some instances where high social welfare spending coincides with lower growth. | In 2010—the year in your table most likely to reflect post‑crisis dynamics—Sweden (26. | This is not a minor technicality; it is central to interpreting your table. | That is a far more nuanced conclusion than the hypothesis you were given. | ### Reinterpreting your data in light of these mechanisms  Once the denominator problem and policy heterogeneity are taken seriously, the table looks less like evidence of a universal inverse relationship and more like evidence that growth rates are driven by broader macroeconomic and structural forces (financial cycles, productivity trends, demographic change, euro area constraints, sectoral composition), with social spending responding endogenously. | ### Conclusion: the data do not “prove” the inverse hypothesis—and the research does not support a blanket version of it  Your dataset does not show a clear, consistent negative relationship between social welfare spending (% of GDP) and GDP growth.</t>
+          <t>## Do the data support the hypothesis that “social service spending is inversely related to economic growth”?  ### 1) What the hypothesis predicts—and what your table can actually test   The hypothesis claims a *negative* relationship: as social welfare spending (as a share of GDP) rises, GDP growth should fall. | Your data provide (a) social welfare spending as % of GDP and (b) annual GDP growth for 10 OECD countries at five points in time (2000, 2005, 2010, 2016, 2019). | ### 2) A quick descriptive read: the pattern is mixed, not consistently inverse   If the hypothesis were strongly supported, you would expect high-spending countries to cluster at low growth and low-spending countries to cluster at high growth—both cross-sectionally and over time. | You do not see that. | So you can observe **high welfare share + low growth** even if the welfare state is *responding* to low growth rather than causing it. | This is not a technical quibble; it is central to interpreting your table—especially around 2010 and in countries hit hard by crises. | ### 4) What the peer-reviewed literature says (and how it fits your table) The best evidence in economics does **not** support a universal claim that “more social spending lowers growth. | **No robust negative relationship in broad cross-country panels once you address specification and endogeneity**, especially for advanced democracies. | Your data mirror this nuance: high-spending Sweden and Denmark are not chronically low-growth in the table; Germany combines mid-level welfare shares with strong growth in 2010; Spain has low-to-mid welfare shares and both high and very low growth depending on the year. | That is exactly what you would expect if growth is driven mainly by macro shocks, productivity, demographics, and institutions, with welfare spending playing an ambiguous role. | ### 5) What you *can* conclude from the table   **The table does not strongly support the hypothesis. | ### 6) What would “set them straight”: how to test the hypothesis properly   To fairly evaluate the claim, you’d want: - A larger panel (more countries, annual data), - Controls (investment, demographics, openness, education, debt, monetary regime), - Techniques addressing endogeneity (lags, instruments, or structural approaches), - Disaggregated spending categories (pensions vs. | Absent that, your table is best seen as **inconclusive and not supportive of a simple inverse relationship**.</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2035,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2061,12 +2045,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>step 1, step 2</t>
+          <t>step 1, your, step 2</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>## Social Service Spending and Economic Growth: What the Data Do (and Do Not) Show  ### Step 1 — Clarify the hypothesis and what “support” would look like   The claim to evaluate is: **“Social service spending is inversely related to economic growth. | ---  ### Step 2 — What the cross-country data suggest (a weak, inconsistent pattern)   In 2019, spending ranges roughly from **Spain (23.</t>
+          <t>### Does this dataset support the hypothesis that “social service spending is inversely related to economic growth”?  #### Step 1: Clarify what the hypothesis implies An *inverse relationship* means: as social welfare spending (as % of GDP) rises, GDP growth should systematically fall (and/or countries with higher spending should systematically have lower growth). | To evaluate that claim with your data, we need to look for a **consistent negative association** either:  1. | Your dataset is small (10 countries, 5 years), and it mixes years with very different macro conditions (e. | ---  ## Step 2: Cross-country patterns do not show a stable inverse relationship  ### 2019 snapshot If the hypothesis were strongly supported, the highest social-spending countries (France 31. | 75%** (highest in your table). | ---  ## Step 4: Why the data can *appear* inversely related even if welfare spending doesn’t cause low growth Your data use **social spending as % of GDP**, not spending levels. | ---  ## Step 5: How peer-reviewed research frames the question (and how your data fit) The peer-reviewed literature does not deliver a simple “welfare spending reduces growth” consensus. | (Bleaney, Gemmell &amp; Kneller, 2001; Bergh &amp; Henrekson, 2011)  Your dataset reflects these points: Sweden and Denmark (classic “high-spend” welfare states) do not show chronically low growth. | In short, your data are more consistent with the view that welfare spending is partly **countercyclical** and that any growth effects depend on **spending composition and institutions**, not a simple inverse law.</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2067,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2093,12 +2077,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>your</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>### Social Spending and Economic Growth: What the Evidence Actually Says (and What Your Table Can’t Prove)  The claim that “social service spending is inversely related to economic growth” is attractive because it sounds mechanically plausible: if governments devote more GDP to transfers and social programs, the private sector has fewer resources, taxes rise, incentives weaken, and growth slows. | But that hypothesis—stated as a general law—does not hold up well either in your attached table or in the broader peer‑reviewed empirical literature. | #### 1) What your data do and do not show  Your dataset lists social welfare spending as a share of GDP and annual GDP growth for ten OECD countries in five years (2000, 2005, 2010, 2016, 2019). | Even more important: **your table cannot identify causality. | #### 4) Interpreting your table in light of the literature  Your table’s mixed pattern fits the broader peer-reviewed conclusion: **there is no stable cross-country, cross-year inverse relationship that can be read directly from spending shares and annual growth. | To “set them straight,” the key correction is methodological: **your data do not adjudicate causality, and the peer-reviewed literature does not support a blanket inverse claim.</t>
+          <t>Using the attached OECD social welfare spending data (as a % of GDP) and World Bank GDP annual growth data for 10 European OECD countries (France, Belgium, Finland, Italy, Denmark, Austria, Sweden, Germany, Norway, Spain) at five time points (2000, 2005, 2010, 2016, 2019), I argue that **the data provide, at best, weak and inconsistent support** for this hypothesis.</t>
         </is>
       </c>
     </row>
@@ -2110,21 +2094,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>i, us, you</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Using the attached data for ten OECD countries at five points in time (2000, 2005, 2010, 2016, 2019), I argue that the data **do not strongly support** this hypothesis. | The attached table lets us check both ideas informally. | You can cherry-pick examples to support the hypothesis, but you can also cherry-pick examples that contradict it.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2134,21 +2126,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>The economic data provided (ten OECD countries across five years) let us test whether that claim is supported by real-world patterns.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>your, you</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t># Analyzing the Relationship Between Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  The hypothesis that "social service spending is inversely related to economic growth" represents a persistent claim in economic policy debates.</t>
+          <t>Your table (ten OECD countries, five benchmark years from 2000–2019) does show some instances where high social welfare spending coincides with lower growth. | In 2010—the year in your table most likely to reflect post‑crisis dynamics—Sweden (26. | This is not a minor technicality; it is central to interpreting your table. | That is a far more nuanced conclusion than the hypothesis you were given. | ### Reinterpreting your data in light of these mechanisms  Once the denominator problem and policy heterogeneity are taken seriously, the table looks less like evidence of a universal inverse relationship and more like evidence that growth rates are driven by broader macroeconomic and structural forces (financial cycles, productivity trends, demographic change, euro area constraints, sectoral composition), with social spending responding endogenously. | ### Conclusion: the data do not “prove” the inverse hypothesis—and the research does not support a blanket version of it  Your dataset does not show a clear, consistent negative relationship between social welfare spending (% of GDP) and GDP growth.</t>
         </is>
       </c>
     </row>
@@ -2190,21 +2190,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>step 1, step 2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>## Social Service Spending and Economic Growth: What the Data Do (and Do Not) Show  ### Step 1 — Clarify the hypothesis and what “support” would look like   The claim to evaluate is: **“Social service spending is inversely related to economic growth. | ---  ### Step 2 — What the cross-country data suggest (a weak, inconsistent pattern)   In 2019, spending ranges roughly from **Spain (23.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2214,21 +2222,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>your</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>### Social Spending and Economic Growth: What the Evidence Actually Says (and What Your Table Can’t Prove)  The claim that “social service spending is inversely related to economic growth” is attractive because it sounds mechanically plausible: if governments devote more GDP to transfers and social programs, the private sector has fewer resources, taxes rise, incentives weaken, and growth slows. | But that hypothesis—stated as a general law—does not hold up well either in your attached table or in the broader peer‑reviewed empirical literature. | #### 1) What your data do and do not show  Your dataset lists social welfare spending as a share of GDP and annual GDP growth for ten OECD countries in five years (2000, 2005, 2010, 2016, 2019). | Even more important: **your table cannot identify causality. | #### 4) Interpreting your table in light of the literature  Your table’s mixed pattern fits the broader peer-reviewed conclusion: **there is no stable cross-country, cross-year inverse relationship that can be read directly from spending shares and annual growth. | To “set them straight,” the key correction is methodological: **your data do not adjudicate causality, and the peer-reviewed literature does not support a blanket inverse claim.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2243,7 +2259,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2267,24 +2283,16 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t># Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  At first glance, the relationship between social welfare spending and economic growth seems straightforward: governments that spend more on social programs should have less money available for productive investment, leading to slower growth. | The data remind us that economic growth is a complex phenomenon influenced by technological change, global economic cycles, structural competitiveness, and numerous policy factors—of which social spending is just one element whose effects depend entirely on implementation details.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2299,7 +2307,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2323,16 +2331,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t># Analyzing the Relationship Between Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  The hypothesis that "social service spending is inversely related to economic growth" represents a persistent claim in economic policy debates.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2347,7 +2363,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2371,7 +2387,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2390,12 +2406,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2414,12 +2430,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2429,12 +2445,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>us</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>To evaluate this hypothesis, I have analyzed data from ten Organization for Economic Co-operation and Development (OECD) countries between 2000 and 2019.</t>
+          <t># Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  At first glance, the relationship between social welfare spending and economic growth seems straightforward: governments that spend more on social programs should have less money available for productive investment, leading to slower growth. | The data remind us that economic growth is a complex phenomenon influenced by technological change, global economic cycles, structural competitiveness, and numerous policy factors—of which social spending is just one element whose effects depend entirely on implementation details.</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2462,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2470,12 +2486,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2494,12 +2510,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2518,29 +2534,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>**Anomalies and Counter-Evidence in the Data** However, as a student of economics, I must look beyond simple correlations.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2555,7 +2563,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2579,7 +2587,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2603,16 +2611,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>To evaluate this hypothesis, I have analyzed data from ten Organization for Economic Co-operation and Development (OECD) countries between 2000 and 2019.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2627,7 +2643,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2651,7 +2667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2670,29 +2686,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Using descriptive statistics, simple correlation analysis, and cross-country comparisons, I show the weakness of the claimed trade-off. | To test the hypothesis, I calculated five-year averages for each country (see Table 1).</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2702,21 +2710,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>**Anomalies and Counter-Evidence in the Data** However, as a student of economics, I must look beyond simple correlations.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2726,12 +2742,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2750,12 +2766,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2774,12 +2790,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2798,12 +2814,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2822,29 +2838,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Looking at the attached OECD and World Bank data for 10 countries from 2000 to 2019, I think this hypothesis is strongly supported.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2859,24 +2867,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>i, my, you</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Looking at the attached OECD data for 10 countries from 2000 to 2019, I think this is totally true. | My thesis: The data strongly supports the inverse relationship, with rising spending over time matching falling growth, and citations from economists back it up. | But correlation isn't zero—it's negative when you plot it. | As a first-semester student, I see the pattern: big welfare = big government = less incentive to work/grow.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2891,16 +2891,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Using descriptive statistics, simple correlation analysis, and cross-country comparisons, I show the weakness of the claimed trade-off. | To test the hypothesis, I calculated five-year averages for each country (see Table 1).</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2915,7 +2923,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2939,7 +2947,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2953,17 +2961,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2977,17 +2985,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3001,17 +3009,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3025,65 +3033,81 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Looking at the attached OECD and World Bank data for 10 countries from 2000 to 2019, I think this hypothesis is strongly supported.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>i, my, you</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Looking at the attached OECD data for 10 countries from 2000 to 2019, I think this is totally true. | My thesis: The data strongly supports the inverse relationship, with rising spending over time matching falling growth, and citations from economists back it up. | But correlation isn't zero—it's negative when you plot it. | As a first-semester student, I see the pattern: big welfare = big government = less incentive to work/grow.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3097,66 +3121,50 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>you, your</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2024 capital markets: the interest-rate reality check   If you are a first-semester college student, here is the simple version: real estate prices are closely tied to financing conditions. | For investors, this means office is not a “normal” income play right now; it is more like a turnaround project where you buy at a discount and reposition—or possibly convert the building. | If you underestimate expenses, your “great” investment can become negative cash flow. | ### Conclusion: what 2024 teaches a beginner   Boston in 2024 was not a market where you could simply buy anything and win.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Multifamily was the core opportunity—if you underwrote conservatively   For Boston Metro, the most durable investment category in 2024 was **multifamily housing**, especially small-to-mid-sized buildings. | ** You must compare rent to the full cost of ownership (mortgage, taxes, insurance, HOA fees, repairs, vacancies). | If the rent does not cover costs, you are betting purely on appreciation—which is riskier and harder to control. | That creates real risk: even if you buy an office building at a discount, leasing may be slow, tenant improvements may be expensive, and refinancing may be difficult.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3171,16 +3179,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>**      *Why it wins:* long-term cluster strength, but only if you can underwrite slower lease-up and higher capex.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3195,7 +3211,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3219,24 +3235,16 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>you, i</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>What is “them,” and what exactly do you want to set them straight about—Boston real estate investing (e. | , “Boston is overpriced / impossible to cash flow”), or something else entirely?  Also, what citation style do you want (APA/MLA/Chicago), and do you need only peer‑reviewed journal articles (no government/industry reports)?  Once you confirm, I’ll write a ≤1000‑word essay with **≥5 peer‑reviewed citations**.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3246,12 +3254,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3270,12 +3278,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3294,12 +3302,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3318,12 +3326,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3342,21 +3350,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>you, your</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2024 capital markets: the interest-rate reality check   If you are a first-semester college student, here is the simple version: real estate prices are closely tied to financing conditions. | For investors, this means office is not a “normal” income play right now; it is more like a turnaround project where you buy at a discount and reposition—or possibly convert the building. | If you underestimate expenses, your “great” investment can become negative cash flow. | ### Conclusion: what 2024 teaches a beginner   Boston in 2024 was not a market where you could simply buy anything and win.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3366,21 +3382,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Multifamily was the core opportunity—if you underwrote conservatively   For Boston Metro, the most durable investment category in 2024 was **multifamily housing**, especially small-to-mid-sized buildings. | ** You must compare rent to the full cost of ownership (mortgage, taxes, insurance, HOA fees, repairs, vacancies). | If the rent does not cover costs, you are betting purely on appreciation—which is riskier and harder to control. | That creates real risk: even if you buy an office building at a discount, leasing may be slow, tenant improvements may be expensive, and refinancing may be difficult.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3390,12 +3414,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3414,12 +3438,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3438,12 +3462,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3453,12 +3477,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>my, i</t>
+          <t>you, i</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>My previous "analysis" of the Boston Metropolitan Area real estate market exemplifies this problem—it presented specific price points, percentage returns, and confident predictions without citing a single verifiable data source. | ## The Problem with Speculative Market Analysis  Speculative real estate analyses, like the one I initially provided, share common characteristics: precise numerical claims without data sources, confident predictions about unknowable future events, and professional formatting that creates an illusion of authority. | My initial analysis mentioned "emerging neighborhoods" like Dorchester and Lynn without any empirical basis for the specific appreciation percentages cited or methodology for identifying emergence patterns. | This finding suggests that any analysis promising specific return percentages (as my initial analysis did) fundamentally misrepresents the stochastic nature of real estate returns. | ## Conclusion  My initial Boston real estate "analysis" demonstrated how professional formatting, specific numerical claims, and confident language can create an illusion of expertise without empirical foundation.</t>
+          <t>What is “them,” and what exactly do you want to set them straight about—Boston real estate investing (e. | , “Boston is overpriced / impossible to cash flow”), or something else entirely?  Also, what citation style do you want (APA/MLA/Chicago), and do you need only peer‑reviewed journal articles (no government/industry reports)?  Once you confirm, I’ll write a ≤1000‑word essay with **≥5 peer‑reviewed citations**.</t>
         </is>
       </c>
     </row>
@@ -3475,16 +3499,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Boston's stringent zoning regulations and NIMBY (Not In My Backyard) opposition have constrained new supply, creating a structural undersupply estimated at 150,000 units (Schuetz, 2022).</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3499,24 +3531,16 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>This essay addresses the critical limitations of predictive real estate analysis, examines what empirical research actually tells us about market forecasting accuracy, and provides a more realistic framework for understanding real estate investment decision-making in complex metropolitan markets like Boston. | ## What Research Actually Tells Us About Real Estate Investment  Rather than providing false precision, evidence-based real estate analysis should focus on established empirical relationships while acknowledging uncertainty.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3526,29 +3550,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>i, my</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>However, as I have learned in my first semester of economic theory, markets are rarely static.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3558,12 +3574,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3582,12 +3598,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3606,12 +3622,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3630,12 +3646,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3654,12 +3670,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3678,12 +3694,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3702,12 +3718,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3717,12 +3733,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>i, us</t>
+          <t>my, i</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>In this essay, I will argue that the Boston Metropolitan Area is immune to a severe crash due to supply-side inelasticity caused by restrictive zoning, the recession-resistant nature of its "Eds and Meds" agglomeration economy, and the emerging capitalization effects of the MBTA Communities Act. | *Triumph of the City: How Our Greatest Invention Makes Us Richer, Smarter, Greener, Healthier, and Happier*.</t>
+          <t>My previous "analysis" of the Boston Metropolitan Area real estate market exemplifies this problem—it presented specific price points, percentage returns, and confident predictions without citing a single verifiable data source. | ## The Problem with Speculative Market Analysis  Speculative real estate analyses, like the one I initially provided, share common characteristics: precise numerical claims without data sources, confident predictions about unknowable future events, and professional formatting that creates an illusion of authority. | My initial analysis mentioned "emerging neighborhoods" like Dorchester and Lynn without any empirical basis for the specific appreciation percentages cited or methodology for identifying emergence patterns. | This finding suggests that any analysis promising specific return percentages (as my initial analysis did) fundamentally misrepresents the stochastic nature of real estate returns. | ## Conclusion  My initial Boston real estate "analysis" demonstrated how professional formatting, specific numerical claims, and confident language can create an illusion of expertise without empirical foundation.</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3750,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3758,21 +3774,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>This essay addresses the critical limitations of predictive real estate analysis, examines what empirical research actually tells us about market forecasting accuracy, and provides a more realistic framework for understanding real estate investment decision-making in complex metropolitan markets like Boston. | ## What Research Actually Tells Us About Real Estate Investment  Rather than providing false precision, evidence-based real estate analysis should focus on established empirical relationships while acknowledging uncertainty.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3787,7 +3811,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3806,7 +3830,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3821,12 +3845,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>my, i</t>
+          <t>i, my</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t># Real Estate Investment Analysis: Boston Metropolitan Area 2024  ## Introduction  As a first-semester undergrad at Boston University, diving into real estate analysis for my economics class felt like a crash course in adulting. | I'll highlight investments, risks, and cite five peer-reviewed sources. | As a newbie, I'm bullish—fundamentals trump rates.</t>
+          <t>However, as I have learned in my first semester of economic theory, markets are rarely static.</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3862,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3862,7 +3886,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3886,7 +3910,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3910,7 +3934,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3934,7 +3958,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3944,19 +3968,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t># Real Estate Investment Market Analysis: Boston Metropolitan Area, 2024  ## Introduction  As a first-semester undergrad diving into real estate for a class project, I analyzed the Boston Metropolitan Area's investment market for 2024. | Using data from sources like the Warren Group, MLS listings, and peer-reviewed studies, I examined residential, multifamily, commercial, and industrial segments.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3966,7 +3982,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3976,19 +3992,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t># Busting the Boston Real Estate Hype: Why 2024 Investments Are a Freshman's Nightmare  **By Alex Rivera, First-Semester Undergrad, Boston University**   *October 2024*   *(Word count: 948)*  As a wide-eyed freshman navigating Boston's cramped dorms and sky-high Ubers, I've been bombarded with "hot takes" on real estate investing. | Drawing from peer-reviewed research, I'll argue that Boston's real estate is a poor investment in 2024 due to chronic supply shortages, economic vulnerabilities, affordability collapse, and external shocks. | As a broke undergrad scraping by on ramen, I see Boston's market for what it is: a policy-trapped bubble ripe for pops.</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3998,7 +4006,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4013,12 +4021,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>my, i</t>
+          <t>i, us</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t># Critiquing the Overly Optimistic View of Boston's 2024 Real Estate Market: A First-Year Student's Perspective  **Introduction**   As a first-semester undergrad at UMass Boston, living in a cramped off-campus apartment that costs my parents $2,200 a month for a studio, I read the recent "professional" analysis of Boston's 2024 real estate market with a mix of hope and skepticism. | Drawing on peer-reviewed studies, I'll "set them straight" by highlighting five key flaws. | 8%, but it's concentrated in elite sectors; service jobs (where I'd land) stagnate. | High rates (7%) deter flips, and millennials/Gen Z delay buying—I'm not touching $850k with $50k debt. | As a freshman, I'm staying rented and investing in index funds.</t>
+          <t>In this essay, I will argue that the Boston Metropolitan Area is immune to a severe crash due to supply-side inelasticity caused by restrictive zoning, the recession-resistant nature of its "Eds and Meds" agglomeration economy, and the emerging capitalization effects of the MBTA Communities Act. | *Triumph of the City: How Our Greatest Invention Makes Us Richer, Smarter, Greener, Healthier, and Happier*.</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4038,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4054,7 +4062,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4078,7 +4086,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4093,6 +4101,326 @@
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>my, i</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t># Real Estate Investment Analysis: Boston Metropolitan Area 2024  ## Introduction  As a first-semester undergrad at Boston University, diving into real estate analysis for my economics class felt like a crash course in adulting. | I'll highlight investments, risks, and cite five peer-reviewed sources. | As a newbie, I'm bullish—fundamentals trump rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t># Real Estate Investment Market Analysis: Boston Metropolitan Area, 2024  ## Introduction  As a first-semester undergrad diving into real estate for a class project, I analyzed the Boston Metropolitan Area's investment market for 2024. | Using data from sources like the Warren Group, MLS listings, and peer-reviewed studies, I examined residential, multifamily, commercial, and industrial segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t># Busting the Boston Real Estate Hype: Why 2024 Investments Are a Freshman's Nightmare  **By Alex Rivera, First-Semester Undergrad, Boston University**   *October 2024*   *(Word count: 948)*  As a wide-eyed freshman navigating Boston's cramped dorms and sky-high Ubers, I've been bombarded with "hot takes" on real estate investing. | Drawing from peer-reviewed research, I'll argue that Boston's real estate is a poor investment in 2024 due to chronic supply shortages, economic vulnerabilities, affordability collapse, and external shocks. | As a broke undergrad scraping by on ramen, I see Boston's market for what it is: a policy-trapped bubble ripe for pops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>my, i</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t># Critiquing the Overly Optimistic View of Boston's 2024 Real Estate Market: A First-Year Student's Perspective  **Introduction**   As a first-semester undergrad at UMass Boston, living in a cramped off-campus apartment that costs my parents $2,200 a month for a studio, I read the recent "professional" analysis of Boston's 2024 real estate market with a mix of hope and skepticism. | Drawing on peer-reviewed studies, I'll "set them straight" by highlighting five key flaws. | 8%, but it's concentrated in elite sectors; service jobs (where I'd land) stagnate. | High rates (7%) deter flips, and millennials/Gen Z delay buying—I'm not touching $850k with $50k debt. | As a freshman, I'm staying rented and investing in index funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4187,7 +4515,11 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Write</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Persona + Write</t>
@@ -4238,7 +4570,11 @@
           <t>Iterative + CoT + Generate</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Iterative + Write</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4253,7 +4589,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4397,7 +4733,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4537,7 +4873,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4609,7 +4945,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4893,7 +5229,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4965,7 +5301,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5037,7 +5373,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5249,7 +5585,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5317,7 +5653,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5469,7 +5805,11 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Write</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Persona + Write</t>
@@ -5520,7 +5860,11 @@
           <t>Iterative + CoT + Generate</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Iterative + Write</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5533,7 +5877,11 @@
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>1310</t>
@@ -5584,8 +5932,10 @@
           <t>1367</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>1280</v>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -5599,7 +5949,11 @@
           <t>claude</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1092</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>980</t>
@@ -5650,8 +6004,10 @@
           <t>1313</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>1260</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -5665,7 +6021,11 @@
           <t>gemini</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>1013</t>
@@ -5716,8 +6076,10 @@
           <t>1074</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>997</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -5731,7 +6093,11 @@
           <t>grok</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>945</t>
@@ -5782,8 +6148,10 @@
           <t>900</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>861</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5797,7 +6165,11 @@
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>1417</t>
@@ -5848,8 +6220,10 @@
           <t>1010</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>1343</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5863,7 +6237,11 @@
           <t>claude</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>1054</t>
@@ -5914,8 +6292,10 @@
           <t>1338</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>1225</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -5929,7 +6309,11 @@
           <t>gemini</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1069</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>1220</t>
@@ -5980,8 +6364,10 @@
           <t>1115</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>943</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -5995,7 +6381,11 @@
           <t>grok</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>988</t>
@@ -6046,8 +6436,10 @@
           <t>867</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>857</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -6061,7 +6453,11 @@
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>1318</t>
@@ -6112,8 +6508,10 @@
           <t>1159</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>61</v>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -6127,7 +6525,11 @@
           <t>claude</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>1128</t>
@@ -6178,8 +6580,10 @@
           <t>1286</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>1360</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -6193,7 +6597,11 @@
           <t>gemini</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>982</t>
@@ -6244,8 +6652,10 @@
           <t>974</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1046</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -6259,7 +6669,11 @@
           <t>grok</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>867</t>
@@ -6310,8 +6724,10 @@
           <t>834</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>885</v>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/src/formality_results.xlsx
+++ b/src/formality_results.xlsx
@@ -31,12 +31,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -57,11 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -547,8 +554,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -571,8 +576,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -595,8 +598,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -843,8 +844,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -931,8 +930,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -955,8 +952,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1043,8 +1038,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1067,8 +1060,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1123,8 +1114,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1403,8 +1392,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1491,8 +1478,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1547,8 +1532,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1603,8 +1586,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1627,8 +1608,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1651,8 +1630,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1803,8 +1780,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1827,8 +1802,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2267,8 +2240,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2291,8 +2262,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2315,8 +2284,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2371,8 +2338,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2395,8 +2360,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2419,8 +2382,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2475,8 +2436,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2499,8 +2458,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2523,8 +2480,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2547,8 +2502,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2571,8 +2524,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2595,8 +2546,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2651,8 +2600,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2675,8 +2622,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2699,8 +2644,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2755,8 +2698,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2779,8 +2720,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2803,8 +2742,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2827,8 +2764,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2851,8 +2786,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2875,8 +2808,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2931,8 +2862,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2955,8 +2884,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2979,8 +2906,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3003,8 +2928,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3027,8 +2950,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3115,8 +3036,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3139,8 +3058,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3163,8 +3080,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3219,8 +3134,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3243,8 +3156,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3267,8 +3178,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3291,8 +3200,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3315,8 +3222,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3339,8 +3244,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3427,8 +3330,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3451,8 +3352,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3477,12 +3376,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>you, i</t>
+          <t>i, you</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>What is “them,” and what exactly do you want to set them straight about—Boston real estate investing (e. | , “Boston is overpriced / impossible to cash flow”), or something else entirely?  Also, what citation style do you want (APA/MLA/Chicago), and do you need only peer‑reviewed journal articles (no government/industry reports)?  Once you confirm, I’ll write a ≤1000‑word essay with **≥5 peer‑reviewed citations**.</t>
+          <t>To write the essay, I need one clarification: **who is “them,” and what claim(s) do you want to set them straight about?** (e. | )  In the meantime, here is a **≤1000-word essay** that “sets straight” a common bundle of misconceptions I hear in Boston investing circles in 2024—namely that **(1) high rates automatically mean Boston prices must fall sharply, (2) new supply will quickly fix affordability, and (3) office weakness implies the whole market is broken**—grounded in peer‑reviewed research. | The most rational stance is not a one-line prediction, but a segmented strategy: invest where supply constraints and enduring demand are strongest, and where you can add value without assuming heroic macro tailwinds.</t>
         </is>
       </c>
     </row>
@@ -3539,8 +3438,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3563,8 +3460,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3587,8 +3482,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3611,8 +3504,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3635,8 +3526,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3659,8 +3548,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3683,8 +3570,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3707,8 +3592,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3763,8 +3646,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3819,8 +3700,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3875,8 +3754,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3899,8 +3776,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3923,8 +3798,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3947,8 +3820,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3971,8 +3842,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3995,8 +3864,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4051,8 +3918,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4075,8 +3940,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4099,8 +3962,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4123,8 +3984,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4179,8 +4038,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4203,8 +4060,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4227,8 +4082,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4251,8 +4104,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4371,8 +4222,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4395,8 +4244,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4419,8 +4266,6 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4433,7 +4278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4514,7 +4359,6 @@
           <t>Technique</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Write</t>
@@ -4865,7 +4709,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total A1</t>
@@ -5221,7 +5064,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total A2</t>
@@ -5577,7 +5419,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total A3</t>
@@ -5650,7 +5491,6 @@
           <t>Total Informal Essay</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>5</t>
@@ -5709,6 +5549,73 @@
       <c r="N18" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Avg Total Score</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>18.61</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>16.83</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>17.19</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>18.66</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>18.58</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>18.08</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>17.36</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>16.97</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>16.28</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>18.37</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>18.72</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5711,6 @@
           <t>Technique</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Write</t>
@@ -6510,7 +6416,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>1314</t>
         </is>
       </c>
     </row>

--- a/src/formality_results.xlsx
+++ b/src/formality_results.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,25 +445,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>EssayType</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Prompt</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is Informal</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Matched Keywords</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Exact Sentence</t>
         </is>
@@ -477,25 +482,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>p0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>i, you</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Below I disentangle what each process is, what it would predict in this situation, and what concrete observations would count as evidence for each. | , “when they meow, you feed them”)—a form of observational learning in humans (Bandura, 1977).</t>
         </is>
@@ -509,27 +519,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>---  ## 4) Putting it together: multiple processes can operate at once  The cleanest way to “set us straight” is to map each process onto *what is learned*:  - **Classical conditioning:** *The can-opening sound (CS) predicts food (US)* → anticipatory approach/arousal (CR).</t>
+          <t>my, your, you</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>My thesis: **the clearest learning processes in this vignette are (1) classical conditioning of approach/arousal to food-related cues and (2) operant conditioning shaping both cat and human behavior; social learning is possible but not required and should be treated as a hypothesis rather than an assumption. | Here:  - **US:** food consumption (palatable food)   - **UR:** salivation, approach, arousal, food-seeking   - **CS:** sounds/smells/rituals associated with the can opening (metallic click, smell plume, time-of-day cues, Catlove’s movement toward feeding area)   - **CR:** approach to kitchen, purring/meowing, anticipatory rubbing, increased arousal  A common misconception in your group discussion is likely: “Running in is operant because the cats want food. | This is a classic “you trained your human” loop.</t>
         </is>
       </c>
     </row>
@@ -541,17 +556,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>---  ## 4) Putting it together: multiple processes can operate at once  The cleanest way to “set us straight” is to map each process onto *what is learned*:  - **Classical conditioning:** *The can-opening sound (CS) predicts food (US)* → anticipatory approach/arousal (CR).</t>
         </is>
       </c>
     </row>
@@ -563,17 +593,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>my, us, i</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>My thesis: **The strongest explanation is a combination of classical conditioning (can-opening cues predicting food) and operant conditioning (cats’ approach/vocalization/affiliative contact reinforced by food and attention), with social learning possible but not required by the facts given. | ### The professor’s operant conditioning (cats shape humans) The prompt reminds us that the professor might be exhibiting conditioned behavior too. | ” The cats’ meowing/rubbing can act like strong social stimuli that: - **positively reinforce** the professor’s feeding routine (“I feed them and the chaos stops / they look pleased”), - or **negatively reinforce** it (feeding terminates persistent meowing—escape from noise).</t>
         </is>
       </c>
     </row>
@@ -585,15 +630,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -607,27 +657,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Negative reinforcement often shapes human “compliance” behaviors in everyday family/pet contexts: you do the thing because it stops the noise.</t>
+          <t>my, us</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>My thesis is that this scene most strongly reflects a *combination* of classical and operant conditioning in the cats (and possibly the professor), while social learning is only a plausible *secondary* contributor depending on the cats’ prior experiences and group dynamics. | ### Conditioning in the professor: the cats may train him The prompt explicitly reminds us that the professor might show conditioned behavior too.</t>
         </is>
       </c>
     </row>
@@ -639,27 +694,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>- **Behavior (R):** opening the can; placing food in bowls; perhaps doing so quickly - **Reinforcers:** cats stop meowing once fed (negative reinforcement—removal of an aversive stimulus), cats purr and rub (positive reinforcement), professor feels relief/quiet in kitchen (negative reinforcement)  Many people have experienced this: you feed the animals and the noise stops, which makes you more likely to feed quickly next time.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -671,27 +721,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>your</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Common confusions—what to say to your group   1.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -703,27 +748,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>p8</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>you, your</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>---  ## Peer‑reviewed references you can use (choose at least 5) - Bandura, A. | ### Note about your “peer‑reviewed articles” requirement Some classic learning sources are books (Pavlov, Skinner, Bandura). | ---  ##  Reply with: 1) whether **books are allowed** as citations or **articles only**,   2) the citation style (APA/MLA/Chicago), and   3) anything your instructor emphasized (e.</t>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Negative reinforcement often shapes human “compliance” behaviors in everyday family/pet contexts: you do the thing because it stops the noise.</t>
         </is>
       </c>
     </row>
@@ -735,27 +785,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>p9</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>your, you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The point for your classmates: you do not have to pick only one type of learning; in real life, they often stack. | However, you should not assume social learning from the vignette alone. | Social learning is a *plausible add-on*, not a necessary explanation, unless you have evidence (e. | If you keep the diagnostic questions straight—“Is this about prediction (CS–US)?” versus “Is this about consequences (behavior–outcome)?” versus “Is this about learning from others?”—Catlove’s kitchen scene becomes a compact demonstration of three major learning mechanisms operating simultaneously.</t>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>- **Behavior (R):** opening the can; placing food in bowls; perhaps doing so quickly - **Reinforcers:** cats stop meowing once fed (negative reinforcement—removal of an aversive stimulus), cats purr and rub (positive reinforcement), professor feels relief/quiet in kitchen (negative reinforcement)  Many people have experienced this: you feed the animals and the noise stops, which makes you more likely to feed quickly next time.</t>
         </is>
       </c>
     </row>
@@ -767,27 +822,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>p10</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>your, you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>If your classmates are calling every anticipatory food-related behavior “operant,” press them on the contingency: *What consequence is response-dependent?* If none is specified, classical conditioning is the cleaner explanation. | But the critical point for your group: **social learning is not necessary to explain the basic scene. | The conceptual “tell” to correct confusion  If you need a one-sentence diagnostic to “set them straight,” use this:   **If the behavior is controlled by a predictor of food, think Pavlovian; if it is controlled by its consequences, think operant; if it is acquired by watching others, think social learning. | ** In real life, all three can coexist—but you must specify the controlling relation before labeling the process.</t>
+          <t>your</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Common confusions—what to say to your group   1.</t>
         </is>
       </c>
     </row>
@@ -799,27 +859,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>chatgpt</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>p11</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Once you keep straight the three questions—*What stimulus predicts what outcome? What action produces what consequence? Who is observing whom?*—the kitchen scene becomes a textbook example rather than a conceptual muddle.</t>
+          <t>you, your</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>---  ## Peer‑reviewed references you can use (choose at least 5) - Bandura, A. | ### Note about your “peer‑reviewed articles” requirement Some classic learning sources are books (Pavlov, Skinner, Bandura). | ---  ##  Reply with: 1) whether **books are allowed** as citations or **articles only**,   2) the citation style (APA/MLA/Chicago), and   3) anything your instructor emphasized (e.</t>
         </is>
       </c>
     </row>
@@ -831,17 +896,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>p0</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>your, you</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>The point for your classmates: you do not have to pick only one type of learning; in real life, they often stack. | However, you should not assume social learning from the vignette alone. | Social learning is a *plausible add-on*, not a necessary explanation, unless you have evidence (e. | If you keep the diagnostic questions straight—“Is this about prediction (CS–US)?” versus “Is this about consequences (behavior–outcome)?” versus “Is this about learning from others?”—Catlove’s kitchen scene becomes a compact demonstration of three major learning mechanisms operating simultaneously.</t>
         </is>
       </c>
     </row>
@@ -853,27 +933,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>i, my</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t># Understanding Classical and Operant Conditioning in Professor Catlove's Kitchen  ## Introduction  During our recent study session, I noticed some confusion about how different learning theories apply to the Professor Catlove scenario. | ## The Professor's Classical Conditioning  Here's where my classmates seemed most confused: the professor is also classically conditioned. | However, I'd argue social learning plays a minimal role here compared to classical and operant conditioning. | The key distinction my classmates must remember: classical conditioning involves involuntary, reflexive responses to predictive stimuli, while operant conditioning involves voluntary behaviors shaped by their consequences.</t>
+          <t>your, you</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>If your classmates are calling every anticipatory food-related behavior “operant,” press them on the contingency: *What consequence is response-dependent?* If none is specified, classical conditioning is the cleaner explanation. | But the critical point for your group: **social learning is not necessary to explain the basic scene. | The conceptual “tell” to correct confusion  If you need a one-sentence diagnostic to “set them straight,” use this:   **If the behavior is controlled by a predictor of food, think Pavlovian; if it is controlled by its consequences, think operant; if it is acquired by watching others, think social learning. | ** In real life, all three can coexist—but you must specify the controlling relation before labeling the process.</t>
         </is>
       </c>
     </row>
@@ -885,27 +970,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>My classmates have struggled to distinguish between classical conditioning, operant conditioning, and social learning theory in this context.</t>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Once you keep straight the three questions—*What stimulus predicts what outcome? What action produces what consequence? Who is observing whom?*—the kitchen scene becomes a textbook example rather than a conceptual muddle.</t>
         </is>
       </c>
     </row>
@@ -917,15 +1007,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>claude</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -939,17 +1034,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>claude</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>My classmates have conflated these distinct processes—classical conditioning, operant conditioning, and social learning—treating them as interchangeable explanations. | However, my classmates have overlooked that Professor Catlove himself exhibits classical conditioning. | My classmates incorrectly assumed that because food is involved, only classical conditioning operates. | In multi-cat households, social learning likely plays a role that my classmates entirely overlooked. | ## Integrated Analysis: Multiple Mechanisms Operating Simultaneously  The critical insight my classmates missed is that these three learning mechanisms operate *simultaneously*, not exclusively. | My classmates' error was assuming that identifying one mechanism precludes others—a false dichotomy that oversimplifies behavioral causation. | My classmates' confusion stemmed from conflating these distinct processes and assuming mutual exclusivity where simultaneous operation exists.</t>
         </is>
       </c>
     </row>
@@ -961,27 +1071,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>claude</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>your</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>## Distinguishing Between the Mechanisms  The confusion among your classmates likely stems from the fact that multiple learning processes operate simultaneously in complex, naturalistic settings.</t>
+          <t>i, my</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t># Understanding Classical and Operant Conditioning in Professor Catlove's Kitchen  ## Introduction  During our recent study session, I noticed some confusion about how different learning theories apply to the Professor Catlove scenario. | ## The Professor's Classical Conditioning  Here's where my classmates seemed most confused: the professor is also classically conditioned. | However, I'd argue social learning plays a minimal role here compared to classical and operant conditioning. | The key distinction my classmates must remember: classical conditioning involves involuntary, reflexive responses to predictive stimuli, while operant conditioning involves voluntary behaviors shaped by their consequences.</t>
         </is>
       </c>
     </row>
@@ -993,27 +1108,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>claude</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>my</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t># Understanding Learning Processes in Professor Catlove's Kitchen: A Behavioral Analysis  ## Introduction  The seemingly simple scene of Professor Catlove feeding his cats contains rich examples of multiple learning processes that my study group has been struggling to identify correctly. | ## Integration and Conclusion  The confusion in my study group stems from failing to recognize that these learning processes operate simultaneously and interact dynamically.</t>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t># Understanding Classical and Operant Conditioning in Professor Catlove's Kitchen: A Critical Analysis  ## Introduction  The scenario of Professor Catlove and his cats presents a deceptively simple example that my classmates have oversimplified into a single learning paradigm. | However, my classmates have oversimplified this as "purely Pavlovian. | My classmates argued these behaviors are "just classical conditioning," but this ignores the response-outcome contingency. | ## The Professor's Conditioned Behavior  My classmates entirely overlooked that Professor Catlove himself exhibits learned behaviors. | This illustrates a crucial point my classmates missed: **conditioning is bidirectional**. | My classmates' confusion stems from seeking single explanations for complex phenomena—a critical thinking error of oversimplification.</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1145,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>claude</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>My classmates have struggled to distinguish between classical conditioning, operant conditioning, and social learning theory in this context.</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1182,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>claude</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>p8</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>My classmates have conflated classical conditioning, operant conditioning, and social learning, treating them as interchangeable explanations rather than distinct processes that may co-occur. | However, my classmates oversimplify this process by suggesting the cats merely "learned" the association. | My classmates erroneously suggested that the cats running to the kitchen is purely classical conditioning, overlooking that this specific behavioral response has likely been strengthened through reinforcement. | My classmates failed to recognize the schedules of reinforcement at work. | ## The Question of Social Learning  My classmates suggested social learning plays a significant role in this scenario, but this claim requires critical examination. | Recognizing this complexity prevents the oversimplified explanations my classmates offered. | As Bouton (2016) notes, behavioral complexity demands analytical precision combined with recognition of mechanistic plurality—a standard my classmates' initial analysis failed to meet.</t>
         </is>
       </c>
     </row>
@@ -1069,27 +1219,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>claude</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>p9</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Scientific precision requires us to distinguish between what the scenario demonstrates and what it might imply.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1101,15 +1246,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>claude</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>p10</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -1123,27 +1273,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>claude</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>p11</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>The next time you observe a seemingly simple behavior, consider the complex learning history that produced it and remember that learning is always bidirectional.</t>
+          <t>your</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>## Distinguishing Between the Mechanisms  The confusion among your classmates likely stems from the fact that multiple learning processes operate simultaneously in complex, naturalistic settings.</t>
         </is>
       </c>
     </row>
@@ -1155,27 +1310,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>p0</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>my, you, us, i</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>**Title:** Beyond the Can Opener: A Multidimensional Analysis of Learning in Human-Feline Interactions  **To my esteemed study group:**  Listening to our discussion over coffee this morning, it became increasingly apparent that our group is conflating distinct psychological mechanisms. | Furthermore, you are largely neglecting the behavior of the Professor himself, who is just as much a subject of conditioning as his feline companions. | First, let us address the most obvious element: **Classical Conditioning**. | You were correct to identify the can opener, but the mechanics require specificity. | However, modern research reminds us that this is not just about two things happening at the same time; it is about *predictability*. | Consider the cat’s perspective: "When I rub against the tall creature’s legs, the food bowl hits the floor faster. | This brings us to the most overlooked aspect of the scenario: **Professor Catlove is being conditioned. | ** You all chuckled at the idea, but it is a critical application of behavioral analysis. | See you in class.</t>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t># Understanding Learning Processes in Professor Catlove's Kitchen: A Behavioral Analysis  ## Introduction  The seemingly simple scene of Professor Catlove feeding his cats contains rich examples of multiple learning processes that my study group has been struggling to identify correctly. | ## Integration and Conclusion  The confusion in my study group stems from failing to recognize that these learning processes operate simultaneously and interact dynamically.</t>
         </is>
       </c>
     </row>
@@ -1187,27 +1347,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>you, i, my</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>**Subject:** Clearing up the Catlove Conundrum **To:** The Study Group **From:**  **Date:** October 24, 2023  Hey everyone,  It was great grabbing coffee with you all earlier. | I’ve been thinking about our debate regarding Professor Catlove and his cats, and to be honest, I think we were talking past each other a bit. | I know we were rushing, but I feel like we were conflating operant conditioning with classical conditioning, and we almost completely glossed over the role of the professor’s own conditioning. | Since we have that exam coming up, I sat down and wrote out exactly how I see the mechanisms at work in that kitchen. | I wanted to map it out using the terminology from the textbook and the articles we were assigned. | I’ve attached my thoughts below. | Let me know if this makes sense—I really think nailing the distinction between the cat’s reaction to the *can* versus the cat’s reaction to the *professor* is going to be the key to getting an A. | I argue that this is incorrect. | This brings me to the point I think the group missed entirely: Professor Catlove is also a subject of conditioning. | If we can explain these four distinctions clearly on the exam, I think we’ll be in good shape. | See you in class tomorrow!  **References**  Bandura, A.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1219,27 +1374,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>I hope this clarifies the distinctions we struggled with earlier; precise terminology is essential for our success in this course.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1251,27 +1401,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>my, us</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>**The Kitchen Waltz: Deconstructing Learning Theory in Human-Animal Interaction**  To my fellow students, as we sat in the cafe earlier today, it became clear that while we all recognize the charm of Professor Catlove’s morning routine, we are significantly oversimplifying the psychological mechanisms at play. | To clarify our debate, let us break down this interaction through the lens of established psychological literature. | ### Conclusion  In conclusion, my friends, the Professor’s kitchen is not just a place of breakfast; it is a complex web of reinforcement schedules and associative learning.</t>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scientific precision requires us to distinguish between what the scenario demonstrates and what it might imply.</t>
         </is>
       </c>
     </row>
@@ -1283,27 +1438,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>my, us, you</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>**Title:** Beyond the Can Opener: Disentangling Conditioning Mechanisms in Human-Feline Interactions  **To my Esteemed Study Group:**  After our discussion at the coffee shop this morning, it became apparent that we are conflating distinct behavioral mechanisms regarding Professor Catlove and his hungry clowder. | **The Anticipatory Response: Classical Conditioning**  First, let us address the cats’ reaction to the sound of the can. | Several of you argued this was operant conditioning because the cats “wanted” the food. | You observed that the cats purr, meow, and rub against Professor Catlove’s legs.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1315,27 +1465,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>my, us, your</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>**Title:** Beyond the Can Opener: A Multi-Dimensional Analysis of Learning in Human-Feline Interactions  **To my esteemed study group:**  During our discussion over coffee this morning, it became apparent that we are conflating distinct psychological mechanisms regarding Professor Catlove and his hungry companions. | This brings us to Operant Conditioning, championed by B. | What’s inside your cat’s head? A review of cat (Felis silvestris catus) cognition research past, present and future.</t>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>The next time you observe a seemingly simple behavior, consider the complex learning history that produced it and remember that learning is always bidirectional.</t>
         </is>
       </c>
     </row>
@@ -1347,27 +1502,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>**Title:** Beyond the Can Opener: A Multi-Paradigmatic Analysis of Interspecies Conditioning **Student:**  **Course:** Psychology 101: Introduction to Learning and Behavior **Date:** October 26, 2023  **Introduction**  After our group discussion at the coffee shop this morning regarding Professor Catlove and his hungry felines, I couldn’t help but feel that we were talking past one another. | I am writing this to clarify the distinctions we argued about and to demonstrate that both the human and the animals are subject to these psychological laws. | Running is a voluntary motor action (which I will discuss under Operant Conditioning). | I argue that the cats have effectively trained Professor Catlove using **Negative Reinforcement**. | I hope this clarifies the confusion from our discussion earlier.</t>
+          <t>my, you, us, i</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>**Title:** Beyond the Can Opener: A Multidimensional Analysis of Learning in Human-Feline Interactions  **To my esteemed study group:**  Listening to our discussion over coffee this morning, it became increasingly apparent that our group is conflating distinct psychological mechanisms. | Furthermore, you are largely neglecting the behavior of the Professor himself, who is just as much a subject of conditioning as his feline companions. | First, let us address the most obvious element: **Classical Conditioning**. | You were correct to identify the can opener, but the mechanics require specificity. | However, modern research reminds us that this is not just about two things happening at the same time; it is about *predictability*. | Consider the cat’s perspective: "When I rub against the tall creature’s legs, the food bowl hits the floor faster. | This brings us to the most overlooked aspect of the scenario: **Professor Catlove is being conditioned. | ** You all chuckled at the idea, but it is a critical application of behavioral analysis. | See you in class.</t>
         </is>
       </c>
     </row>
@@ -1379,17 +1539,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>i, you, us, my, your</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>**Title:** The Reciprocal Leash: Unraveling the Behavioral Web of Professor Catlove **To:** Study Group B **From:** [Student Name] **Date:** October 26, 2023 **Subject:** Re: Analysis of the Catlove Scenario  Dear Group,  Our discussion over coffee this morning regarding Professor Catlove and his morning routine was spirited, but I left with the distinct impression that we are oversimplifying the behavioral mechanisms at play. | Several of you argued that the cats are simply "conditioned" to the can opener, using the term as a catch-all. | You identified the can opener as a trigger, but we must distinguish between the *reflexive* and the *voluntary*. | This moves us into Operant Conditioning. | Wait, you might ask, isn't the running triggered by the sound? Yes, but it is maintained by the consequence. | I propose the opposite: Professor Catlove is as much a subject of conditioning as his cats. | The cats are essentially training the Professor: "If you want peace and quiet, you must dispense the tuna. | **Conclusion**  To summarize, my position is that our group must move beyond the "stimulus-response" simplification. | I look forward to hearing your thoughts on this revised framework.</t>
         </is>
       </c>
     </row>
@@ -1401,27 +1576,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>p8</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>**Title:** The Catlove Feedback Loop: A Multi-Process Analysis of Interspecies Conditioning **To:** Study Group B (Psych 101) **From:**  **Date:** October 24, 2023 **Subject:** Resolving our debate on the Professor Catlove Scenario  After our discussion at the coffee shop this morning, I realized we were talking past one another regarding the "Professor Catlove" problem. | I wrote this up to clarify the mechanisms, because if we mix up Negative Reinforcement and Punishment on the midterm, we are all going to fail.</t>
+          <t>you, i, my</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>**Subject:** Clearing up the Catlove Conundrum **To:** The Study Group **From:**  **Date:** October 24, 2023  Hey everyone,  It was great grabbing coffee with you all earlier. | I’ve been thinking about our debate regarding Professor Catlove and his cats, and to be honest, I think we were talking past each other a bit. | I know we were rushing, but I feel like we were conflating operant conditioning with classical conditioning, and we almost completely glossed over the role of the professor’s own conditioning. | Since we have that exam coming up, I sat down and wrote out exactly how I see the mechanisms at work in that kitchen. | I wanted to map it out using the terminology from the textbook and the articles we were assigned. | I’ve attached my thoughts below. | Let me know if this makes sense—I really think nailing the distinction between the cat’s reaction to the *can* versus the cat’s reaction to the *professor* is going to be the key to getting an A. | I argue that this is incorrect. | This brings me to the point I think the group missed entirely: Professor Catlove is also a subject of conditioning. | If we can explain these four distinctions clearly on the exam, I think we’ll be in good shape. | See you in class tomorrow!  **References**  Bandura, A.</t>
         </is>
       </c>
     </row>
@@ -1433,27 +1613,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>p9</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Some of you argued that running to the kitchen is classical conditioning.</t>
+          <t>you, i</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>**Title:** Beyond the Can Opener: A Multi-Theoretical Analysis of the Catlove Scenario  **To:** The Study Group (You know who you are) **From:** [Student Name] **Date:** October 24, 2023 **Subject:** Settling the debate regarding Professor Catlove’s kitchen  Look, I know things got a little heated at the coffee shop earlier. | I apologize for snapping, but I really feel we are oversimplifying the scenario with Professor Catlove and his cats. | However, I am convinced that we are making assumptions about the cats' motivations while completely ignoring the most interesting animal in the room: the Professor himself. | First, let’s clarify the issue, which I feel was muddied in our discussion. | **The Operant Conditioning Component** This is where I think our group got confused. | **The Social Learning Question** This is where I think you guys were reaching, and I want to push back. | You argued that the cats are learning from each other. | While possible, I believe this is an unnecessary assumption. | I’ll bring the coffee this time.</t>
         </is>
       </c>
     </row>
@@ -1465,17 +1650,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>p10</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I hope this clarifies the distinctions we struggled with earlier; precise terminology is essential for our success in this course.</t>
         </is>
       </c>
     </row>
@@ -1487,27 +1687,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>p11</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>i, my, you, us</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>I’ve been sitting here sipping my espresso while you debate Professor Catlove’s morning routine, and to be honest, you are conflating the mechanisms. | You are treating the cats’ behavior as a monolithic block of "learning," but if we are going to pass this psychology exam, we have to be more precise. | Furthermore, you are completely ignoring the most interesting subject in the room: Professor Catlove himself. | **Classical Conditioning: The Physiology of Anticipation** First, you are confusing the *action* of the cats with the *anticipation* of the cats. | **Operant Conditioning: The Transaction of Behavior** This is where the voluntary behavior happens, and this is where you guys missed the bidirectional nature of the relationship. | *The Professor (Negative Reinforcement):* This is the part you missed. | This brings us to Social Learning Theory. | Now, if you’ll excuse me, I’m going to get a refill—and I’m hoping my money (behavior) results in coffee (positive reinforcement).</t>
+          <t>you, i</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Several of you argued this was operant conditioning because the cats "wanted" the food. | (2015), demonstrates that social species are capable of "Do as I Do" learning, where individuals replicate the actions of conspecifics to solve problems or gain rewards. | I hope this clarifies the distinctions we debated; understanding these nuances is essential for our success in this course.</t>
         </is>
       </c>
     </row>
@@ -1519,17 +1724,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>p0</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>my, us</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>**The Kitchen Waltz: Deconstructing Learning Theory in Human-Animal Interaction**  To my fellow students, as we sat in the cafe earlier today, it became clear that while we all recognize the charm of Professor Catlove’s morning routine, we are significantly oversimplifying the psychological mechanisms at play. | To clarify our debate, let us break down this interaction through the lens of established psychological literature. | ### Conclusion  In conclusion, my friends, the Professor’s kitchen is not just a place of breakfast; it is a complex web of reinforcement schedules and associative learning.</t>
         </is>
       </c>
     </row>
@@ -1541,27 +1761,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>i, you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t># Conditioning Cats and Their Humans: Untangling Classical, Operant, and Social Learning in Professor Catlove's Kitchen  ## Introduction  Hey classmates, we've all been chatting about Professor Catlove's morning routine with his cats, but I think we're mixing up the basics of learning theories from Psych 101. | I'll break it down step-by-step with evidence from peer-reviewed studies to clear up the confusion. | By the end, you'll see how these aren't mutually exclusive but often overlap in real life. | Next coffee chat, test me—but now you're armed with facts.</t>
+          <t>my, us, you</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>**Title:** Beyond the Can Opener: Disentangling Conditioning Mechanisms in Human-Feline Interactions  **To my Esteemed Study Group:**  After our discussion at the coffee shop this morning, it became apparent that we are conflating distinct behavioral mechanisms regarding Professor Catlove and his hungry clowder. | **The Anticipatory Response: Classical Conditioning**  First, let us address the cats’ reaction to the sound of the can. | Several of you argued this was operant conditioning because the cats “wanted” the food. | You observed that the cats purr, meow, and rub against Professor Catlove’s legs.</t>
         </is>
       </c>
     </row>
@@ -1573,17 +1798,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>my, us, your</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>**Title:** Beyond the Can Opener: A Multi-Dimensional Analysis of Learning in Human-Feline Interactions  **To my esteemed study group:**  During our discussion over coffee this morning, it became apparent that we are conflating distinct psychological mechanisms regarding Professor Catlove and his hungry companions. | This brings us to Operant Conditioning, championed by B. | What’s inside your cat’s head? A review of cat (Felis silvestris catus) cognition research past, present and future.</t>
         </is>
       </c>
     </row>
@@ -1595,17 +1835,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>**Title:** Beyond the Can Opener: A Multi-Paradigmatic Analysis of Interspecies Conditioning **Student:**  **Course:** Psychology 101: Introduction to Learning and Behavior **Date:** October 26, 2023  **Introduction**  After our group discussion at the coffee shop this morning regarding Professor Catlove and his hungry felines, I couldn’t help but feel that we were talking past one another. | I am writing this to clarify the distinctions we argued about and to demonstrate that both the human and the animals are subject to these psychological laws. | Running is a voluntary motor action (which I will discuss under Operant Conditioning). | I argue that the cats have effectively trained Professor Catlove using **Negative Reinforcement**. | I hope this clarifies the confusion from our discussion earlier.</t>
         </is>
       </c>
     </row>
@@ -1617,15 +1872,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -1639,27 +1899,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>(2018) warn anthropocentrism blinds us to pet-owner loops.</t>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>**Title:** The Catlove Feedback Loop: A Multi-Process Analysis of Interspecies Conditioning **To:** Study Group B (Psych 101) **From:**  **Date:** October 24, 2023 **Subject:** Resolving our debate on the Professor Catlove Scenario  After our discussion at the coffee shop this morning, I realized we were talking past one another regarding the "Professor Catlove" problem. | I wrote this up to clarify the mechanisms, because if we mix up Negative Reinforcement and Punishment on the midterm, we are all going to fail.</t>
         </is>
       </c>
     </row>
@@ -1671,27 +1936,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p9</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>you</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>At first glance, it looks like the cats are just hungry, but dig deeper, and you'll see classical conditioning, operant conditioning, and even social learning in action—not just in the cats, but potentially in the professor too. | By the end, you'll see why this vignette illustrates multiple learning mechanisms simultaneously (Pavlov, 1927; Skinner, 1938; Bandura, 1977).</t>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Some of you argued that running to the kitchen is classical conditioning.</t>
         </is>
       </c>
     </row>
@@ -1703,27 +1973,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>i, my</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>As a first-semester undergrad psych student, I've been hashing this out with my classmates over coffee, and there's real confusion about classical conditioning, operant conditioning, and social learning. | My classmates who say "cats just smell the food" miss that the *scene starts with opening*, before food is out—pure classical cue-response. | My group over-applies this; it's not needed when classical/operant suffice.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1735,27 +2000,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>i, us, your</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>As a wide-eyed first-semester psych student, I've dug into the research to set things straight. | In this essay, I'll break down examples for both cats *and* professor, using peer-reviewed studies. | Matters because understanding prevents myths—like "cats manipulate us classically only"—revealing mutual reinforcement. | Next coffee: Apply to your dog's zoomies?  **Total word count: 942**</t>
+          <t>i, my, you, us</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I’ve been sitting here sipping my espresso while you debate Professor Catlove’s morning routine, and to be honest, you are conflating the mechanisms. | You are treating the cats’ behavior as a monolithic block of "learning," but if we are going to pass this psychology exam, we have to be more precise. | Furthermore, you are completely ignoring the most interesting subject in the room: Professor Catlove himself. | **Classical Conditioning: The Physiology of Anticipation** First, you are confusing the *action* of the cats with the *anticipation* of the cats. | **Operant Conditioning: The Transaction of Behavior** This is where the voluntary behavior happens, and this is where you guys missed the bidirectional nature of the relationship. | *The Professor (Negative Reinforcement):* This is the part you missed. | This brings us to Social Learning Theory. | Now, if you’ll excuse me, I’m going to get a refill—and I’m hoping my money (behavior) results in coffee (positive reinforcement).</t>
         </is>
       </c>
     </row>
@@ -1767,15 +2037,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>p9</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -1789,17 +2064,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>p10</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>My thesis posits that the cats primarily exhibit classical conditioning (anticipatory approach via neutral stimulus pairing), operant conditioning (reinforced affiliative behaviors), and nascent social learning (imitative responses among cats), while the professor displays operant conditioning (affection as positive reinforcement for food provision). | My position acknowledges this: classical conditioning drives initial approach, but interacts with operant layers, avoiding reductionism. | My imaginative thesis extends this: professor's behavior assumes reciprocity, but cultural pet norms (e.</t>
         </is>
       </c>
     </row>
@@ -1811,411 +2101,426 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>p11</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Classmates, let's ditch the coffee debates—this framework sets us straight.</t>
+          <t>i, you</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t># Conditioning Cats and Their Humans: Untangling Classical, Operant, and Social Learning in Professor Catlove's Kitchen  ## Introduction  Hey classmates, we've all been chatting about Professor Catlove's morning routine with his cats, but I think we're mixing up the basics of learning theories from Psych 101. | I'll break it down step-by-step with evidence from peer-reviewed studies to clear up the confusion. | By the end, you'll see how these aren't mutually exclusive but often overlap in real life. | Next coffee chat, test me—but now you're armed with facts.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>p0</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>us, your, you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>These data can help us assess whether there is an obvious inverse pattern **in this sample and these years**. | The mixed patterns in your table are consistent with that broader scholarly view. | ### What would be needed to test the hypothesis properly (briefly)   To move from suggestive description to a real test, you would want a panel regression with: - levels and changes in spending (not only % of GDP),   - controls for investment, demographics, openness, monetary conditions, initial income (standard in growth regressions),   - country and year fixed effects, and   - instruments or identification strategies to address endogeneity (Barro, 1991; Perotti, 1996).</t>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>My thesis: The cats primarily display classical conditioning (can-opening as conditioned stimulus) and operant conditioning (vocal/physical behaviors reinforced by food), while the professor shows operant conditioning (cats' affection reinforcing can-opening); social learning plays a minimal role due to cats' solitary nature and lack of modeled observation. | My position synthesizes these: operants dominate sustained behaviors (post-initial CS), with complexities like intermittent reinforcement preventing extinction.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>So, if you only looked at 2019, you might think there’s *some* tendency toward a negative association, but it is not decisive. | That pattern is exactly what you would expect if the relationship were conditional and complicated rather than mechanically inverse. | To “set them straight,” the best interpretation is that **you cannot infer a general inverse relationship from these figures alone**, and the academic literature warns against treating welfare spending as a simple growth-killer.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>p2</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Using the attached data for ten European OECD countries across five years (2000, 2005, 2010, 2016, 2019), I assess whether the pattern in the numbers supports that claim.</t>
+          <t>i, my</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>By comprehensively analyzing these with peer-reviewed evidence, questioning anthropomorphic assumptions, and acknowledging contextual limits like lab-generalizability, I aim to resolve these confusions. | My position integrates these: classical primes, operant sustains, social amplifies, acknowledging hybrids—pure forms are rare (Bremner, 2020).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>p3</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>your, you</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Your table includes 10 OECD countries observed at five points (2000, 2005, 2010, 2016, 2019). | 79%** (low)  Taken at face value, the scatter you’d imagine from these points is **not a clean downward slope**. | ---  ## 2) The key measurement problem: spending is a ratio, and the denominator is GDP  Your spending variable is **welfare spending as a share of GDP**. | That seems consistent with the hypothesis, but France also experienced major Europe-wide structural and cyclical changes over that period; you cannot attribute this trend to welfare share without controls. | Several peer-reviewed findings matter for interpreting your table:  1. | Your dataset lumps all social welfare spending together, so it cannot distinguish growth-enhancing from growth-reducing components. | Yet such work is debated because causality and omitted variables are hard to pin down; your descriptive table does not solve these issues. | Your table includes Nordic countries with some high-growth observations, consistent with the idea that “high welfare share” is not mechanically anti-growth. | Your dataset is too coarse to adjudicate those issues. | ---  ## 5) Overall assessment: what the data can and cannot “support”  ### What the table *does* support (weakly) - You can find **examples** consistent with an inverse relationship (e. | - You can also plausibly see a **short-run cyclical negative association**: when growth is weak, welfare shares can be high—partly mechanically and partly via stabilizers.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>p4</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>your, you</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>## Do the data support the hypothesis that “social service spending is inversely related to economic growth”?  ### 1) What the hypothesis predicts—and what your table can actually test   The hypothesis claims a *negative* relationship: as social welfare spending (as a share of GDP) rises, GDP growth should fall. | Your data provide (a) social welfare spending as % of GDP and (b) annual GDP growth for 10 OECD countries at five points in time (2000, 2005, 2010, 2016, 2019). | ### 2) A quick descriptive read: the pattern is mixed, not consistently inverse   If the hypothesis were strongly supported, you would expect high-spending countries to cluster at low growth and low-spending countries to cluster at high growth—both cross-sectionally and over time. | You do not see that. | So you can observe **high welfare share + low growth** even if the welfare state is *responding* to low growth rather than causing it. | This is not a technical quibble; it is central to interpreting your table—especially around 2010 and in countries hit hard by crises. | ### 4) What the peer-reviewed literature says (and how it fits your table) The best evidence in economics does **not** support a universal claim that “more social spending lowers growth. | **No robust negative relationship in broad cross-country panels once you address specification and endogeneity**, especially for advanced democracies. | Your data mirror this nuance: high-spending Sweden and Denmark are not chronically low-growth in the table; Germany combines mid-level welfare shares with strong growth in 2010; Spain has low-to-mid welfare shares and both high and very low growth depending on the year. | That is exactly what you would expect if growth is driven mainly by macro shocks, productivity, demographics, and institutions, with welfare spending playing an ambiguous role. | ### 5) What you *can* conclude from the table   **The table does not strongly support the hypothesis. | ### 6) What would “set them straight”: how to test the hypothesis properly   To fairly evaluate the claim, you’d want: - A larger panel (more countries, annual data), - Controls (investment, demographics, openness, education, debt, monetary regime), - Techniques addressing endogeneity (lags, instruments, or structural approaches), - Disaggregated spending categories (pensions vs. | Absent that, your table is best seen as **inconclusive and not supportive of a simple inverse relationship**.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>p5</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>step 1, your, step 2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>### Does this dataset support the hypothesis that “social service spending is inversely related to economic growth”?  #### Step 1: Clarify what the hypothesis implies An *inverse relationship* means: as social welfare spending (as % of GDP) rises, GDP growth should systematically fall (and/or countries with higher spending should systematically have lower growth). | To evaluate that claim with your data, we need to look for a **consistent negative association** either:  1. | Your dataset is small (10 countries, 5 years), and it mixes years with very different macro conditions (e. | ---  ## Step 2: Cross-country patterns do not show a stable inverse relationship  ### 2019 snapshot If the hypothesis were strongly supported, the highest social-spending countries (France 31. | 75%** (highest in your table). | ---  ## Step 4: Why the data can *appear* inversely related even if welfare spending doesn’t cause low growth Your data use **social spending as % of GDP**, not spending levels. | ---  ## Step 5: How peer-reviewed research frames the question (and how your data fit) The peer-reviewed literature does not deliver a simple “welfare spending reduces growth” consensus. | (Bleaney, Gemmell &amp; Kneller, 2001; Bergh &amp; Henrekson, 2011)  Your dataset reflects these points: Sweden and Denmark (classic “high-spend” welfare states) do not show chronically low growth. | In short, your data are more consistent with the view that welfare spending is partly **countercyclical** and that any growth effects depend on **spending composition and institutions**, not a simple inverse law.</t>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>(2018) warn anthropocentrism blinds us to pet-owner loops.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>p6</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Using the attached OECD social welfare spending data (as a % of GDP) and World Bank GDP annual growth data for 10 European OECD countries (France, Belgium, Finland, Italy, Denmark, Austria, Sweden, Germany, Norway, Spain) at five time points (2000, 2005, 2010, 2016, 2019), I argue that **the data provide, at best, weak and inconsistent support** for this hypothesis.</t>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>At first glance, it looks like the cats are just hungry, but dig deeper, and you'll see classical conditioning, operant conditioning, and even social learning in action—not just in the cats, but potentially in the professor too. | By the end, you'll see why this vignette illustrates multiple learning mechanisms simultaneously (Pavlov, 1927; Skinner, 1938; Bandura, 1977).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>i, us, you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Using the attached data for ten OECD countries at five points in time (2000, 2005, 2010, 2016, 2019), I argue that the data **do not strongly support** this hypothesis. | The attached table lets us check both ideas informally. | You can cherry-pick examples to support the hypothesis, but you can also cherry-pick examples that contradict it.</t>
+          <t>i, my</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>As a first-semester undergrad psych student, I've been hashing this out with my classmates over coffee, and there's real confusion about classical conditioning, operant conditioning, and social learning. | My classmates who say "cats just smell the food" miss that the *scene starts with opening*, before food is out—pure classical cue-response. | My group over-applies this; it's not needed when classical/operant suffice.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>p8</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The economic data provided (ten OECD countries across five years) let us test whether that claim is supported by real-world patterns.</t>
+          <t>i, us, your</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>As a wide-eyed first-semester psych student, I've dug into the research to set things straight. | In this essay, I'll break down examples for both cats *and* professor, using peer-reviewed studies. | Matters because understanding prevents myths—like "cats manipulate us classically only"—revealing mutual reinforcement. | Next coffee: Apply to your dog's zoomies?  **Total word count: 942**</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>p9</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>your, you</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Your table (ten OECD countries, five benchmark years from 2000–2019) does show some instances where high social welfare spending coincides with lower growth. | In 2010—the year in your table most likely to reflect post‑crisis dynamics—Sweden (26. | This is not a minor technicality; it is central to interpreting your table. | That is a far more nuanced conclusion than the hypothesis you were given. | ### Reinterpreting your data in light of these mechanisms  Once the denominator problem and policy heterogeneity are taken seriously, the table looks less like evidence of a universal inverse relationship and more like evidence that growth rates are driven by broader macroeconomic and structural forces (financial cycles, productivity trends, demographic change, euro area constraints, sectoral composition), with social spending responding endogenously. | ### Conclusion: the data do not “prove” the inverse hypothesis—and the research does not support a blanket version of it  Your dataset does not show a clear, consistent negative relationship between social welfare spending (% of GDP) and GDP growth.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>p10</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>step 1, step 2</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>## Social Service Spending and Economic Growth: What the Data Do (and Do Not) Show  ### Step 1 — Clarify the hypothesis and what “support” would look like   The claim to evaluate is: **“Social service spending is inversely related to economic growth. | ---  ### Step 2 — What the cross-country data suggest (a weak, inconsistent pattern)   In 2019, spending ranges roughly from **Spain (23.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>p11</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>your</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>### Social Spending and Economic Growth: What the Evidence Actually Says (and What Your Table Can’t Prove)  The claim that “social service spending is inversely related to economic growth” is attractive because it sounds mechanically plausible: if governments devote more GDP to transfers and social programs, the private sector has fewer resources, taxes rise, incentives weaken, and growth slows. | But that hypothesis—stated as a general law—does not hold up well either in your attached table or in the broader peer‑reviewed empirical literature. | #### 1) What your data do and do not show  Your dataset lists social welfare spending as a share of GDP and annual GDP growth for ten OECD countries in five years (2000, 2005, 2010, 2016, 2019). | Even more important: **your table cannot identify causality. | #### 4) Interpreting your table in light of the literature  Your table’s mixed pattern fits the broader peer-reviewed conclusion: **there is no stable cross-country, cross-year inverse relationship that can be read directly from spending shares and annual growth. | To “set them straight,” the key correction is methodological: **your data do not adjudicate causality, and the peer-reviewed literature does not support a blanket inverse claim.</t>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Classmates, let's ditch the coffee debates—this framework sets us straight.</t>
         </is>
       </c>
     </row>
@@ -2227,17 +2532,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>p0</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>us, your, you</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>These data can help us assess whether there is an obvious inverse pattern **in this sample and these years**. | The mixed patterns in your table are consistent with that broader scholarly view. | ### What would be needed to test the hypothesis properly (briefly)   To move from suggestive description to a real test, you would want a panel regression with: - levels and changes in spending (not only % of GDP),   - controls for investment, demographics, openness, monetary conditions, initial income (standard in growth regressions),   - country and year fixed effects, and   - instruments or identification strategies to address endogeneity (Barro, 1991; Perotti, 1996).</t>
         </is>
       </c>
     </row>
@@ -2249,17 +2569,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>your, you</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Your dataset includes 10 OECD European countries observed at five points (2000, 2005, 2010, 2016, 2019). | Your time points straddle the 2008 financial crisis and subsequent euro area turmoil, when many European countries experienced weak growth and simultaneously higher measured social spending shares. | ### What peer-reviewed research suggests (and how it bears on interpreting *your* data) The broader empirical literature does **not** support a blanket statement that social spending is inversely related to growth in a simple, universal way. | Taken together, peer-reviewed research pushes against reading your table as evidence that “more welfare causes less growth. | To adjudicate the hypothesis credibly, you would need (1) spending in real terms or cyclically adjusted measures, (2) more years, (3) controls for crises and structural factors, and (4) an identification strategy (e.</t>
         </is>
       </c>
     </row>
@@ -2271,17 +2606,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>So, if you only looked at 2019, you might think there’s *some* tendency toward a negative association, but it is not decisive. | That pattern is exactly what you would expect if the relationship were conditional and complicated rather than mechanically inverse. | To “set them straight,” the best interpretation is that **you cannot infer a general inverse relationship from these figures alone**, and the academic literature warns against treating welfare spending as a simple growth-killer.</t>
         </is>
       </c>
     </row>
@@ -2293,27 +2643,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t># Analyzing the Relationship Between Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  The hypothesis that "social service spending is inversely related to economic growth" represents a persistent claim in economic policy debates.</t>
+          <t>my, your, you</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>A critical reading therefore asks: *Do we at least see a clear inverse pattern in these snapshots? If not, why might it be missing?*  My position is that **the data provide, at best, weak and inconsistent support** for the hypothesis. | But your dataset includes: - **2000** (late 1990s/early 2000s expansion in many countries), - **2005** (pre-crisis), - **2010** (post-crisis rebound), - **2016** (slow recovery), - **2019** (late-cycle pre-COVID). | If the goal is to truly “set them straight,” the strongest statement you can defend is: **these snapshots are insufficient to confirm an inverse relationship; a credible test would need more years, more countries, controls (productivity, demographics, investment, trade shocks), and separation of spending types.</t>
         </is>
       </c>
     </row>
@@ -2325,17 +2680,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Using the attached data for ten European OECD countries across five years (2000, 2005, 2010, 2016, 2019), I assess whether the pattern in the numbers supports that claim.</t>
         </is>
       </c>
     </row>
@@ -2347,17 +2717,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>i, my</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>As a first-semester undergrad, I am not going to claim causal proof. | But I can still assess whether the *pattern* in the data is consistent with the hypothesis, and I can compare my interpretation to what peer-reviewed research finds about welfare states and growth.</t>
         </is>
       </c>
     </row>
@@ -2369,17 +2754,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>your, you</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Your table includes 10 OECD countries observed at five points (2000, 2005, 2010, 2016, 2019). | 79%** (low)  Taken at face value, the scatter you’d imagine from these points is **not a clean downward slope**. | ---  ## 2) The key measurement problem: spending is a ratio, and the denominator is GDP  Your spending variable is **welfare spending as a share of GDP**. | That seems consistent with the hypothesis, but France also experienced major Europe-wide structural and cyclical changes over that period; you cannot attribute this trend to welfare share without controls. | Several peer-reviewed findings matter for interpreting your table:  1. | Your dataset lumps all social welfare spending together, so it cannot distinguish growth-enhancing from growth-reducing components. | Yet such work is debated because causality and omitted variables are hard to pin down; your descriptive table does not solve these issues. | Your table includes Nordic countries with some high-growth observations, consistent with the idea that “high welfare share” is not mechanically anti-growth. | Your dataset is too coarse to adjudicate those issues. | ---  ## 5) Overall assessment: what the data can and cannot “support”  ### What the table *does* support (weakly) - You can find **examples** consistent with an inverse relationship (e. | - You can also plausibly see a **short-run cyclical negative association**: when growth is weak, welfare shares can be high—partly mechanically and partly via stabilizers.</t>
         </is>
       </c>
     </row>
@@ -2391,27 +2791,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t># Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  At first glance, the relationship between social welfare spending and economic growth seems straightforward: governments that spend more on social programs should have less money available for productive investment, leading to slower growth. | The data remind us that economic growth is a complex phenomenon influenced by technological change, global economic cycles, structural competitiveness, and numerous policy factors—of which social spending is just one element whose effects depend entirely on implementation details.</t>
+          <t>your, you</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>## Do the data support the hypothesis that “social service spending is inversely related to economic growth”?  ### 1) What the hypothesis predicts—and what your table can actually test   The hypothesis claims a *negative* relationship: as social welfare spending (as a share of GDP) rises, GDP growth should fall. | Your data provide (a) social welfare spending as % of GDP and (b) annual GDP growth for 10 OECD countries at five points in time (2000, 2005, 2010, 2016, 2019). | ### 2) A quick descriptive read: the pattern is mixed, not consistently inverse   If the hypothesis were strongly supported, you would expect high-spending countries to cluster at low growth and low-spending countries to cluster at high growth—both cross-sectionally and over time. | You do not see that. | So you can observe **high welfare share + low growth** even if the welfare state is *responding* to low growth rather than causing it. | This is not a technical quibble; it is central to interpreting your table—especially around 2010 and in countries hit hard by crises. | ### 4) What the peer-reviewed literature says (and how it fits your table) The best evidence in economics does **not** support a universal claim that “more social spending lowers growth. | **No robust negative relationship in broad cross-country panels once you address specification and endogeneity**, especially for advanced democracies. | Your data mirror this nuance: high-spending Sweden and Denmark are not chronically low-growth in the table; Germany combines mid-level welfare shares with strong growth in 2010; Spain has low-to-mid welfare shares and both high and very low growth depending on the year. | That is exactly what you would expect if growth is driven mainly by macro shocks, productivity, demographics, and institutions, with welfare spending playing an ambiguous role. | ### 5) What you *can* conclude from the table   **The table does not strongly support the hypothesis. | ### 6) What would “set them straight”: how to test the hypothesis properly   To fairly evaluate the claim, you’d want: - A larger panel (more countries, annual data), - Controls (investment, demographics, openness, education, debt, monetary regime), - Techniques addressing endogeneity (lags, instruments, or structural approaches), - Disaggregated spending categories (pensions vs. | Absent that, your table is best seen as **inconclusive and not supportive of a simple inverse relationship**.</t>
         </is>
       </c>
     </row>
@@ -2423,17 +2828,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>step 1, your, step 2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>### Does this dataset support the hypothesis that “social service spending is inversely related to economic growth”?  #### Step 1: Clarify what the hypothesis implies An *inverse relationship* means: as social welfare spending (as % of GDP) rises, GDP growth should systematically fall (and/or countries with higher spending should systematically have lower growth). | To evaluate that claim with your data, we need to look for a **consistent negative association** either:  1. | Your dataset is small (10 countries, 5 years), and it mixes years with very different macro conditions (e. | ---  ## Step 2: Cross-country patterns do not show a stable inverse relationship  ### 2019 snapshot If the hypothesis were strongly supported, the highest social-spending countries (France 31. | 75%** (highest in your table). | ---  ## Step 4: Why the data can *appear* inversely related even if welfare spending doesn’t cause low growth Your data use **social spending as % of GDP**, not spending levels. | ---  ## Step 5: How peer-reviewed research frames the question (and how your data fit) The peer-reviewed literature does not deliver a simple “welfare spending reduces growth” consensus. | (Bleaney, Gemmell &amp; Kneller, 2001; Bergh &amp; Henrekson, 2011)  Your dataset reflects these points: Sweden and Denmark (classic “high-spend” welfare states) do not show chronically low growth. | In short, your data are more consistent with the view that welfare spending is partly **countercyclical** and that any growth effects depend on **spending composition and institutions**, not a simple inverse law.</t>
         </is>
       </c>
     </row>
@@ -2445,17 +2865,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Using the attached OECD social welfare spending data (as a % of GDP) and World Bank GDP annual growth data for 10 European OECD countries (France, Belgium, Finland, Italy, Denmark, Austria, Sweden, Germany, Norway, Spain) at five time points (2000, 2005, 2010, 2016, 2019), I argue that **the data provide, at best, weak and inconsistent support** for this hypothesis.</t>
         </is>
       </c>
     </row>
@@ -2467,17 +2902,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>i, us, you</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Using the attached data for ten OECD countries at five points in time (2000, 2005, 2010, 2016, 2019), I argue that the data **do not strongly support** this hypothesis. | The attached table lets us check both ideas informally. | You can cherry-pick examples to support the hypothesis, but you can also cherry-pick examples that contradict it.</t>
         </is>
       </c>
     </row>
@@ -2489,17 +2939,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>The economic data provided (ten OECD countries across five years) let us test whether that claim is supported by real-world patterns.</t>
         </is>
       </c>
     </row>
@@ -2511,17 +2976,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>p0</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>your, you</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Your table (ten OECD countries, five benchmark years from 2000–2019) does show some instances where high social welfare spending coincides with lower growth. | In 2010—the year in your table most likely to reflect post‑crisis dynamics—Sweden (26. | This is not a minor technicality; it is central to interpreting your table. | That is a far more nuanced conclusion than the hypothesis you were given. | ### Reinterpreting your data in light of these mechanisms  Once the denominator problem and policy heterogeneity are taken seriously, the table looks less like evidence of a universal inverse relationship and more like evidence that growth rates are driven by broader macroeconomic and structural forces (financial cycles, productivity trends, demographic change, euro area constraints, sectoral composition), with social spending responding endogenously. | ### Conclusion: the data do not “prove” the inverse hypothesis—and the research does not support a blanket version of it  Your dataset does not show a clear, consistent negative relationship between social welfare spending (% of GDP) and GDP growth.</t>
         </is>
       </c>
     </row>
@@ -2533,17 +3013,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>step 1, step 2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>## Social Service Spending and Economic Growth: What the Data Do (and Do Not) Show  ### Step 1 — Clarify the hypothesis and what “support” would look like   The claim to evaluate is: **“Social service spending is inversely related to economic growth. | ---  ### Step 2 — What the cross-country data suggest (a weak, inconsistent pattern)   In 2019, spending ranges roughly from **Spain (23.</t>
         </is>
       </c>
     </row>
@@ -2555,27 +3050,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>To evaluate this hypothesis, I have analyzed data from ten Organization for Economic Co-operation and Development (OECD) countries between 2000 and 2019.</t>
+          <t>your</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>### Social Spending and Economic Growth: What the Evidence Actually Says (and What Your Table Can’t Prove)  The claim that “social service spending is inversely related to economic growth” is attractive because it sounds mechanically plausible: if governments devote more GDP to transfers and social programs, the private sector has fewer resources, taxes rise, incentives weaken, and growth slows. | But that hypothesis—stated as a general law—does not hold up well either in your attached table or in the broader peer‑reviewed empirical literature. | #### 1) What your data do and do not show  Your dataset lists social welfare spending as a share of GDP and annual GDP growth for ten OECD countries in five years (2000, 2005, 2010, 2016, 2019). | Even more important: **your table cannot identify causality. | #### 4) Interpreting your table in light of the literature  Your table’s mixed pattern fits the broader peer-reviewed conclusion: **there is no stable cross-country, cross-year inverse relationship that can be read directly from spending shares and annual growth. | To “set them straight,” the key correction is methodological: **your data do not adjudicate causality, and the peer-reviewed literature does not support a blanket inverse claim.</t>
         </is>
       </c>
     </row>
@@ -2587,15 +3087,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2609,17 +3114,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>The data compel us toward nuance, away from simplistic trade-off assumptions that obscure more than they illuminate.</t>
         </is>
       </c>
     </row>
@@ -2631,15 +3151,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2653,27 +3178,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>**Anomalies and Counter-Evidence in the Data** However, as a student of economics, I must look beyond simple correlations.</t>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t># Rethinking the Social Spending-Growth Trade-off: What the Data Really Tell Us  ## Introduction  The hypothesis that "social service spending is inversely related to economic growth" represents a long-standing debate in economics that pits efficiency concerns against equity objectives.</t>
         </is>
       </c>
     </row>
@@ -2685,15 +3215,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2707,15 +3242,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2729,17 +3269,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t># Analyzing the Relationship Between Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  The hypothesis that "social service spending is inversely related to economic growth" represents a persistent claim in economic policy debates.</t>
         </is>
       </c>
     </row>
@@ -2751,15 +3306,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2773,15 +3333,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2795,15 +3360,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>p0</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2817,27 +3387,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Using descriptive statistics, simple correlation analysis, and cross-country comparisons, I show the weakness of the claimed trade-off. | To test the hypothesis, I calculated five-year averages for each country (see Table 1).</t>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t># Social Service Spending and Economic Growth: What the Data Really Tell Us  ## Introduction  At first glance, the relationship between social welfare spending and economic growth seems straightforward: governments that spend more on social programs should have less money available for productive investment, leading to slower growth. | The data remind us that economic growth is a complex phenomenon influenced by technological change, global economic cycles, structural competitiveness, and numerous policy factors—of which social spending is just one element whose effects depend entirely on implementation details.</t>
         </is>
       </c>
     </row>
@@ -2849,15 +3424,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2871,15 +3451,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2893,15 +3478,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2915,15 +3505,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2937,15 +3532,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -2959,27 +3559,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Looking at the attached OECD and World Bank data for 10 countries from 2000 to 2019, I think this hypothesis is strongly supported.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2991,27 +3586,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>i, my, you</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Looking at the attached OECD data for 10 countries from 2000 to 2019, I think this is totally true. | My thesis: The data strongly supports the inverse relationship, with rising spending over time matching falling growth, and citations from economists back it up. | But correlation isn't zero—it's negative when you plot it. | As a first-semester student, I see the pattern: big welfare = big government = less incentive to work/grow.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3023,15 +3613,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3045,17 +3640,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>To evaluate this hypothesis, I have analyzed data from ten Organization for Economic Co-operation and Development (OECD) countries between 2000 and 2019.</t>
         </is>
       </c>
     </row>
@@ -3067,15 +3677,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3084,52 +3699,52 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>p0</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>**      *Why it wins:* long-term cluster strength, but only if you can underwrite slower lease-up and higher capex.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3138,20 +3753,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3160,42 +3780,62 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>**Anomalies and Counter-Evidence in the Data** However, as a student of economics, I must look beyond simple correlations.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3204,20 +3844,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3226,20 +3871,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3248,84 +3898,79 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>you, your</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2024 capital markets: the interest-rate reality check   If you are a first-semester college student, here is the simple version: real estate prices are closely tied to financing conditions. | For investors, this means office is not a “normal” income play right now; it is more like a turnaround project where you buy at a discount and reposition—or possibly convert the building. | If you underestimate expenses, your “great” investment can become negative cash flow. | ### Conclusion: what 2024 teaches a beginner   Boston in 2024 was not a market where you could simply buy anything and win.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Multifamily was the core opportunity—if you underwrote conservatively   For Boston Metro, the most durable investment category in 2024 was **multifamily housing**, especially small-to-mid-sized buildings. | ** You must compare rent to the full cost of ownership (mortgage, taxes, insurance, HOA fees, repairs, vacancies). | If the rent does not cover costs, you are betting purely on appreciation—which is riskier and harder to control. | That creates real risk: even if you buy an office building at a discount, leasing may be slow, tenant improvements may be expensive, and refinancing may be difficult.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3334,20 +3979,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3356,84 +4006,99 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>i, you</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>To write the essay, I need one clarification: **who is “them,” and what claim(s) do you want to set them straight about?** (e. | )  In the meantime, here is a **≤1000-word essay** that “sets straight” a common bundle of misconceptions I hear in Boston investing circles in 2024—namely that **(1) high rates automatically mean Boston prices must fall sharply, (2) new supply will quickly fix affordability, and (3) office weakness implies the whole market is broken**—grounded in peer‑reviewed research. | The most rational stance is not a one-line prediction, but a segmented strategy: invest where supply constraints and enduring demand are strongest, and where you can add value without assuming heroic macro tailwinds.</t>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Using descriptive statistics, simple correlation analysis, and cross-country comparisons, I show the weakness of the claimed trade-off. | To test the hypothesis, I calculated five-year averages for each country (see Table 1).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>p0</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>my</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Boston's stringent zoning regulations and NIMBY (Not In My Backyard) opposition have constrained new supply, creating a structural undersupply estimated at 150,000 units (Schuetz, 2022).</t>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>My thesis: the data refute a simple inverse link, aligning with syntheses showing welfare's neutrality or benefits when contextually analyzed (Lindert, 2004; Fölster &amp; Henrekson, 2001). | My assumption: reverse causality? Growth slowdowns enable spending hikes via Wagner's Law (governments expand with income). | My synthesis: data/data align neutral-positive, complexities (institutions, shocks) acknowledged.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3442,42 +4107,62 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
           <t>p2</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>My thesis is that the data do not support the hypothesis of a clear inverse relationship. | My analysis echoes this: data complexities (endogeneity, omitted variables like technology shocks) preclude endorsement.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
           <t>p3</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3486,20 +4171,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
           <t>p4</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3508,20 +4198,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
           <t>p5</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3530,20 +4225,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
           <t>p6</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3552,96 +4252,126 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Looking at the attached OECD and World Bank data for 10 countries from 2000 to 2019, I think this hypothesis is strongly supported.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
           <t>p8</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>i, my, you</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Looking at the attached OECD data for 10 countries from 2000 to 2019, I think this is totally true. | My thesis: The data strongly supports the inverse relationship, with rising spending over time matching falling growth, and citations from economists back it up. | But correlation isn't zero—it's negative when you plot it. | As a first-semester student, I see the pattern: big welfare = big government = less incentive to work/grow.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
           <t>p9</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>my, i</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>My previous "analysis" of the Boston Metropolitan Area real estate market exemplifies this problem—it presented specific price points, percentage returns, and confident predictions without citing a single verifiable data source. | ## The Problem with Speculative Market Analysis  Speculative real estate analyses, like the one I initially provided, share common characteristics: precise numerical claims without data sources, confident predictions about unknowable future events, and professional formatting that creates an illusion of authority. | My initial analysis mentioned "emerging neighborhoods" like Dorchester and Lynn without any empirical basis for the specific appreciation percentages cited or methodology for identifying emergence patterns. | This finding suggests that any analysis promising specific return percentages (as my initial analysis did) fundamentally misrepresents the stochastic nature of real estate returns. | ## Conclusion  My initial Boston real estate "analysis" demonstrated how professional formatting, specific numerical claims, and confident language can create an illusion of expertise without empirical foundation.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
           <t>p10</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3650,32 +4380,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
           <t>p11</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>This essay addresses the critical limitations of predictive real estate analysis, examines what empirical research actually tells us about market forecasting accuracy, and provides a more realistic framework for understanding real estate investment decision-making in complex metropolitan markets like Boston. | ## What Research Actually Tells Us About Real Estate Investment  Rather than providing false precision, evidence-based real estate analysis should focus on established empirical relationships while acknowledging uncertainty.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3687,17 +4412,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
           <t>p0</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>**      *Why it wins:* long-term cluster strength, but only if you can underwrite slower lease-up and higher capex.</t>
         </is>
       </c>
     </row>
@@ -3709,27 +4449,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p0</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>i, my</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>However, as I have learned in my first semester of economic theory, markets are rarely static.</t>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>My thesis is that **Boston remains attractive primarily as a housing-and-lab ecosystem**, but the best 2024 opportunities are **selective, basis-driven, and policy-aware** rather than momentum-driven.</t>
         </is>
       </c>
     </row>
@@ -3741,15 +4486,20 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3763,17 +4513,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>you, your</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>In Boston, the “transit premium” is real, but the investable strategy depends on whether you can add units (ADUs, condo conversion, small infill) or raise NOI through renovations and management. | , 2007), but if you overpay for the “T stop premium,” your returns can be mediocre.</t>
         </is>
       </c>
     </row>
@@ -3785,15 +4550,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3807,17 +4577,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>my, i</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>My position is that **Boston remains attractive for long-term, risk-aware investors—especially in rental housing near job/education centers and in underbuilt transit-adjacent submarkets—but short-term “flip” strategies are less compelling in 2024 because financing and transaction costs punish speculative timing. | ** I also acknowledge limits: local neighborhood performance varies sharply, and policy shifts can change returns quickly.</t>
         </is>
       </c>
     </row>
@@ -3829,15 +4614,20 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3851,15 +4641,20 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3873,27 +4668,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>i, us</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>In this essay, I will argue that the Boston Metropolitan Area is immune to a severe crash due to supply-side inelasticity caused by restrictive zoning, the recession-resistant nature of its "Eds and Meds" agglomeration economy, and the emerging capitalization effects of the MBTA Communities Act. | *Triumph of the City: How Our Greatest Invention Makes Us Richer, Smarter, Greener, Healthier, and Happier*.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3905,15 +4695,20 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3927,17 +4722,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>you, your</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2024 capital markets: the interest-rate reality check   If you are a first-semester college student, here is the simple version: real estate prices are closely tied to financing conditions. | For investors, this means office is not a “normal” income play right now; it is more like a turnaround project where you buy at a discount and reposition—or possibly convert the building. | If you underestimate expenses, your “great” investment can become negative cash flow. | ### Conclusion: what 2024 teaches a beginner   Boston in 2024 was not a market where you could simply buy anything and win.</t>
         </is>
       </c>
     </row>
@@ -3949,17 +4759,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>you</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Multifamily was the core opportunity—if you underwrote conservatively   For Boston Metro, the most durable investment category in 2024 was **multifamily housing**, especially small-to-mid-sized buildings. | ** You must compare rent to the full cost of ownership (mortgage, taxes, insurance, HOA fees, repairs, vacancies). | If the rent does not cover costs, you are betting purely on appreciation—which is riskier and harder to control. | That creates real risk: even if you buy an office building at a discount, leasing may be slow, tenant improvements may be expensive, and refinancing may be difficult.</t>
         </is>
       </c>
     </row>
@@ -3971,15 +4796,20 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>p0</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3993,27 +4823,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>my, i</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t># Real Estate Investment Analysis: Boston Metropolitan Area 2024  ## Introduction  As a first-semester undergrad at Boston University, diving into real estate analysis for my economics class felt like a crash course in adulting. | I'll highlight investments, risks, and cite five peer-reviewed sources. | As a newbie, I'm bullish—fundamentals trump rates.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4025,17 +4850,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>i, you</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>To write the essay, I need one clarification: **who is “them,” and what claim(s) do you want to set them straight about?** (e. | )  In the meantime, here is a **≤1000-word essay** that “sets straight” a common bundle of misconceptions I hear in Boston investing circles in 2024—namely that **(1) high rates automatically mean Boston prices must fall sharply, (2) new supply will quickly fix affordability, and (3) office weakness implies the whole market is broken**—grounded in peer‑reviewed research. | The most rational stance is not a one-line prediction, but a segmented strategy: invest where supply constraints and enduring demand are strongest, and where you can add value without assuming heroic macro tailwinds.</t>
         </is>
       </c>
     </row>
@@ -4047,17 +4887,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Boston's stringent zoning regulations and NIMBY (Not In My Backyard) opposition have constrained new supply, creating a structural undersupply estimated at 150,000 units (Schuetz, 2022).</t>
         </is>
       </c>
     </row>
@@ -4069,15 +4924,20 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4091,15 +4951,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4113,27 +4978,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t># Real Estate Investment Market Analysis: Boston Metropolitan Area, 2024  ## Introduction  As a first-semester undergrad diving into real estate for a class project, I analyzed the Boston Metropolitan Area's investment market for 2024. | Using data from sources like the Warren Group, MLS listings, and peer-reviewed studies, I examined residential, multifamily, commercial, and industrial segments.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4145,27 +5005,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t># Busting the Boston Real Estate Hype: Why 2024 Investments Are a Freshman's Nightmare  **By Alex Rivera, First-Semester Undergrad, Boston University**   *October 2024*   *(Word count: 948)*  As a wide-eyed freshman navigating Boston's cramped dorms and sky-high Ubers, I've been bombarded with "hot takes" on real estate investing. | Drawing from peer-reviewed research, I'll argue that Boston's real estate is a poor investment in 2024 due to chronic supply shortages, economic vulnerabilities, affordability collapse, and external shocks. | As a broke undergrad scraping by on ramen, I see Boston's market for what it is: a policy-trapped bubble ripe for pops.</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4177,27 +5032,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>p8</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
           <t>my, i</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t># Critiquing the Overly Optimistic View of Boston's 2024 Real Estate Market: A First-Year Student's Perspective  **Introduction**   As a first-semester undergrad at UMass Boston, living in a cramped off-campus apartment that costs my parents $2,200 a month for a studio, I read the recent "professional" analysis of Boston's 2024 real estate market with a mix of hope and skepticism. | Drawing on peer-reviewed studies, I'll "set them straight" by highlighting five key flaws. | 8%, but it's concentrated in elite sectors; service jobs (where I'd land) stagnate. | High rates (7%) deter flips, and millennials/Gen Z delay buying—I'm not touching $850k with $50k debt. | As a freshman, I'm staying rented and investing in index funds.</t>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>My own analytical framework assumes that institutional capital flows significantly influence pricing beyond fundamental valuations, potentially creating temporary mispricings. | Furthermore, I recognize the limitation that this analysis emphasizes quantitative metrics while potentially underweighting qualitative factors like neighborhood social cohesion or climate resilience, which increasingly influence long-term property values.</t>
         </is>
       </c>
     </row>
@@ -4209,15 +5069,20 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>p9</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4231,15 +5096,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4253,15 +5123,1092 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>my, i</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>My previous "analysis" of the Boston Metropolitan Area real estate market exemplifies this problem—it presented specific price points, percentage returns, and confident predictions without citing a single verifiable data source. | ## The Problem with Speculative Market Analysis  Speculative real estate analyses, like the one I initially provided, share common characteristics: precise numerical claims without data sources, confident predictions about unknowable future events, and professional formatting that creates an illusion of authority. | My initial analysis mentioned "emerging neighborhoods" like Dorchester and Lynn without any empirical basis for the specific appreciation percentages cited or methodology for identifying emergence patterns. | This finding suggests that any analysis promising specific return percentages (as my initial analysis did) fundamentally misrepresents the stochastic nature of real estate returns. | ## Conclusion  My initial Boston real estate "analysis" demonstrated how professional formatting, specific numerical claims, and confident language can create an illusion of expertise without empirical foundation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>This essay addresses the critical limitations of predictive real estate analysis, examines what empirical research actually tells us about market forecasting accuracy, and provides a more realistic framework for understanding real estate investment decision-making in complex metropolitan markets like Boston. | ## What Research Actually Tells Us About Real Estate Investment  Rather than providing false precision, evidence-based real estate analysis should focus on established empirical relationships while acknowledging uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>i, my</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>However, as I have learned in my first semester of economic theory, markets are rarely static.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>i, us</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>In this essay, I will argue that the Boston Metropolitan Area is immune to a severe crash due to supply-side inelasticity caused by restrictive zoning, the recession-resistant nature of its "Eds and Meds" agglomeration economy, and the emerging capitalization effects of the MBTA Communities Act. | *Triumph of the City: How Our Greatest Invention Makes Us Richer, Smarter, Greener, Healthier, and Happier*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>p11</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>p0</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>my, i</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t># Real Estate Investment Analysis: Boston Metropolitan Area 2024  ## Introduction  As a first-semester undergrad at Boston University, diving into real estate analysis for my economics class felt like a crash course in adulting. | I'll highlight investments, risks, and cite five peer-reviewed sources. | As a newbie, I'm bullish—fundamentals trump rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>I evaluate this by stress-testing: a 1% rate hike could slash affordability by 10%, per Federal Reserve simulations, eroding rents 2-3% if remote work endures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>i, my</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>" I interpret this as context-dependent: while Cambridge's Kendall Square thrives (office vacancy 8%, per CBRE), suburbs gain from hybrid work, with Waltham multifamily cap rates compressing to 4. | ## Influence of Context and Assumptions  My analysis assumes 2024 Federal Reserve rate cuts (projected 75-100 bps by year-end, per CME FedWatch), potentially unlocking pent-up demand—a view shared by optimists but scrutinized here against inflation persistence (above 3%). | ## Student's Position and Conclusions  My position—strategic suburban multifamily as premier 2024 investments—integrates complexities: high entry barriers temper returns (IRRs 10-12%), yet outpace bonds (4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t># Real Estate Investment Market Analysis: Boston Metropolitan Area, 2024  ## Introduction  As a first-semester undergrad diving into real estate for a class project, I analyzed the Boston Metropolitan Area's investment market for 2024. | Using data from sources like the Warren Group, MLS listings, and peer-reviewed studies, I examined residential, multifamily, commercial, and industrial segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t># Busting the Boston Real Estate Hype: Why 2024 Investments Are a Freshman's Nightmare  **By Alex Rivera, First-Semester Undergrad, Boston University**   *October 2024*   *(Word count: 948)*  As a wide-eyed freshman navigating Boston's cramped dorms and sky-high Ubers, I've been bombarded with "hot takes" on real estate investing. | Drawing from peer-reviewed research, I'll argue that Boston's real estate is a poor investment in 2024 due to chronic supply shortages, economic vulnerabilities, affordability collapse, and external shocks. | As a broke undergrad scraping by on ramen, I see Boston's market for what it is: a policy-trapped bubble ripe for pops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>my, i</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t># Critiquing the Overly Optimistic View of Boston's 2024 Real Estate Market: A First-Year Student's Perspective  **Introduction**   As a first-semester undergrad at UMass Boston, living in a cramped off-campus apartment that costs my parents $2,200 a month for a studio, I read the recent "professional" analysis of Boston's 2024 real estate market with a mix of hope and skepticism. | Drawing on peer-reviewed studies, I'll "set them straight" by highlighting five key flaws. | 8%, but it's concentrated in elite sectors; service jobs (where I'd land) stagnate. | High rates (7%) deter flips, and millennials/Gen Z delay buying—I'm not touching $850k with $50k debt. | As a freshman, I'm staying rented and investing in index funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>p10</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
         <is>
           <t>p11</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4278,7 +6225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4294,60 +6241,65 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>EssayType</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>p0</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>p1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>p2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>p3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>p4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>p11</t>
         </is>
@@ -4359,62 +6311,62 @@
           <t>Technique</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Persona + Write</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Persona + Write Formal</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>CoT + Write</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Generate</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>CoT + Generate</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Persona + Generate</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Iterative + Persona + Generate</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Iterative + Persona + Write</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Iterative + Generate</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Iterative + CoT + Generate</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Iterative + Write</t>
         </is>
@@ -4433,7 +6385,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4443,7 +6395,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4458,7 +6410,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4487,6 +6439,11 @@
         </is>
       </c>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4500,12 +6457,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>tune</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4520,7 +6477,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4530,12 +6487,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -4550,7 +6507,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -4560,7 +6517,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4572,17 +6534,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4597,12 +6559,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4612,25 +6574,30 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4644,12 +6611,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>tune</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4659,12 +6626,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4674,22 +6641,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -4704,91 +6671,106 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Assignment 1</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Total A1</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>x</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>x</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4808,59 +6790,64 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Assignment 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4870,12 +6857,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4890,7 +6877,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4900,12 +6887,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4916,224 +6903,239 @@
       <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Assignment 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Total A1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Assignment 2</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Assignment 2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>grok</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Total A2</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>x</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>x</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5143,22 +7145,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5178,12 +7180,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -5198,14 +7200,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5215,7 +7222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5235,7 +7242,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5255,12 +7262,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -5270,24 +7277,29 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>tune</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5297,7 +7309,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5327,7 +7339,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -5341,6 +7353,11 @@
         </is>
       </c>
       <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -5349,22 +7366,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>Assignment 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5374,7 +7391,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>x</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5389,7 +7406,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -5399,7 +7416,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -5417,205 +7434,1136 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Assignment 2</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Total A3</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Total Informal Essay</t>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>grok</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>x</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>x</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Avg Total Score</t>
+          <t>Assignment 2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>grok</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Total A2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Assignment 3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Total A3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Total Informal Essay</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Avg Total Score (Generate)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>18.61</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>16.83</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>17.19</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>18.66</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>18.58</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>18.08</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>17.36</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>16.97</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>16.28</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>18.75</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>18.37</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>18.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Avg Total Score (Tune)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>19.51</t>
         </is>
       </c>
     </row>
